--- a/reports/셀린느/셀린느_mgf_matched_5_guilds.xlsx
+++ b/reports/셀린느/셀린느_mgf_matched_5_guilds.xlsx
@@ -1199,7 +1199,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%ED%92%8D</t>
   </si>
   <si>
-    <t>1063조 4971억 9740만</t>
+    <t>1086조 8133억 5735만</t>
   </si>
   <si>
     <t>로드숍</t>

--- a/reports/셀린느/셀린느_mgf_matched_5_guilds.xlsx
+++ b/reports/셀린느/셀린느_mgf_matched_5_guilds.xlsx
@@ -371,7 +371,7 @@
     <t>107</t>
   </si>
   <si>
-    <t>573조 9428억 4113만</t>
+    <t>574조 2339억 346만</t>
   </si>
   <si>
     <t>10</t>
@@ -383,7 +383,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%88%EA%BD%83%EC%B2%B4%EB%A6%AC</t>
   </si>
   <si>
-    <t>394조 2073억 8498만</t>
+    <t>445조 451억 1674만</t>
   </si>
   <si>
     <t>11</t>
@@ -443,6 +443,18 @@
     <t>15</t>
   </si>
   <si>
+    <t>냐락셋째</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%85%8B%EC%A7%B8</t>
+  </si>
+  <si>
+    <t>186조 7701억 3305만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>냐락린</t>
   </si>
   <si>
@@ -452,7 +464,7 @@
     <t>170조 6456억 3813만</t>
   </si>
   <si>
-    <t>16</t>
+    <t>17</t>
   </si>
   <si>
     <t>냐락쿠</t>
@@ -464,18 +476,6 @@
     <t>167조 4498억 971만</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>냐락셋째</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%85%8B%EC%A7%B8</t>
-  </si>
-  <si>
-    <t>162조 4589억 7006만</t>
-  </si>
-  <si>
     <t>18</t>
   </si>
   <si>
@@ -1043,7 +1043,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
   </si>
   <si>
-    <t>31조 4660억 7156만</t>
+    <t>31조 8267억 9814만</t>
   </si>
   <si>
     <t>26수빈</t>
@@ -2865,7 +2865,7 @@
         <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>135</v>
@@ -2897,7 +2897,7 @@
         <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>135</v>
@@ -2929,7 +2929,7 @@
         <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>135</v>

--- a/reports/셀린느/셀린느_mgf_matched_5_guilds.xlsx
+++ b/reports/셀린느/셀린느_mgf_matched_5_guilds.xlsx
@@ -1685,7 +1685,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
   </si>
   <si>
-    <t>8602억 3404만</t>
+    <t>9591억 6321만</t>
   </si>
   <si>
     <t>용광사</t>

--- a/reports/셀린느/셀린느_mgf_matched_5_guilds.xlsx
+++ b/reports/셀린느/셀린느_mgf_matched_5_guilds.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">LUXURY!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">LUXURY!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">냐락!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">셀린느!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">이콩!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">이콩!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">호러!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="556">
   <si>
     <t>guild_name</t>
   </si>
@@ -98,280 +98,280 @@
     <t>가입문의 : 닭도리도리탕, 티짐 20조 이상 문의바랍니다.</t>
   </si>
   <si>
+    <t>티짐</t>
+  </si>
+  <si>
+    <t>2026.04.10</t>
+  </si>
+  <si>
+    <t>셀린느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
+  </si>
+  <si>
+    <t>Scania 2</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>2경 38조 753억 677만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>LUXURY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
+  </si>
+  <si>
+    <t>Scania 16</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>2경 2185조 8183억 1617만</t>
+  </si>
+  <si>
+    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
+  </si>
+  <si>
+    <t>살뽀시</t>
+  </si>
+  <si>
+    <t>호러</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%98%B8%EB%9F%AC</t>
+  </si>
+  <si>
+    <t>Scania 10</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>2경 1593조 2154억 9496만</t>
+  </si>
+  <si>
+    <t>오래 하실분들 환영입니다</t>
+  </si>
+  <si>
+    <t>애기요밋</t>
+  </si>
+  <si>
+    <t>이콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>Scania 28</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>4위</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>28명</t>
+  </si>
+  <si>
+    <t>1경 9137조 3448억 6787만</t>
+  </si>
+  <si>
+    <t>가입문의 - 요쯔</t>
+  </si>
+  <si>
+    <t>요쯔</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>냐락불곰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%B6%88%EA%B3%B0</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>1경 2229조 7494억 2484만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>냐락오리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%98%A4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>2154조 8718억 7131만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>썬콜법사님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%AC%EB%8B%98</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>2080조 4719억 3396만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>냐락겅듀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EA%B2%85%EB%93%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>1972조 9857억 9778만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>벽서</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%BD%EC%84%9C</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>1344조 2346억 7402만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>바럄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EB%9F%84</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>875조 7755억 8766만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%A7%90</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>823조 1358억 7794만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>이대팔가르마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8C%80%ED%8C%94%EA%B0%80%EB%A5%B4%EB%A7%88</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>739조 9535억 2604만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>닭도리도리탕</t>
   </si>
   <si>
-    <t>2026.04.10</t>
-  </si>
-  <si>
-    <t>셀린느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
-  </si>
-  <si>
-    <t>Scania 2</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>2경 38조 753억 677만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>LUXURY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
-  </si>
-  <si>
-    <t>Scania 16</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>2경 2185조 8183억 1617만</t>
-  </si>
-  <si>
-    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
-  </si>
-  <si>
-    <t>26워커</t>
-  </si>
-  <si>
-    <t>호러</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%98%B8%EB%9F%AC</t>
-  </si>
-  <si>
-    <t>Scania 10</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>2경 1593조 2154억 9496만</t>
-  </si>
-  <si>
-    <t>오래 하실분들 환영입니다</t>
-  </si>
-  <si>
-    <t>애기요밋</t>
-  </si>
-  <si>
-    <t>이콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>Scania 28</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>4위</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>28명</t>
-  </si>
-  <si>
-    <t>1경 9137조 3448억 6787만</t>
-  </si>
-  <si>
-    <t>가입문의 - 요쯔</t>
-  </si>
-  <si>
-    <t>요쯔</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>냐락불곰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%B6%88%EA%B3%B0</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>1경 2226조 3090억 3853만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>냐락오리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%98%A4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>2154조 8718억 7131만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>썬콜법사님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%AC%EB%8B%98</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>2073조 1808억 4486만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>냐락겅듀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EA%B2%85%EB%93%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>1955조 7041억 7601만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>벽서</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%BD%EC%84%9C</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>1341조 8148억 4992만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>바럄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EB%9F%84</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>753조 6100억 5754만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>이대팔가르마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8C%80%ED%8C%94%EA%B0%80%EB%A5%B4%EB%A7%88</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>713조 5929억 4038만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>티짐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%A7%90</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>692조 6645억 8214만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%AD%EB%8F%84%EB%A6%AC%EB%8F%84%EB%A6%AC%ED%83%95</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>신궁</t>
   </si>
   <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>574조 2339억 346만</t>
+    <t>737조 8866억 8253만</t>
   </si>
   <si>
     <t>10</t>
@@ -383,7 +383,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%88%EA%BD%83%EC%B2%B4%EB%A6%AC</t>
   </si>
   <si>
-    <t>445조 451억 1674만</t>
+    <t>456조 5442억 584만</t>
   </si>
   <si>
     <t>11</t>
@@ -398,7 +398,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>375조 5674억 9688만</t>
+    <t>391조 5083억 9813만</t>
   </si>
   <si>
     <t>12</t>
@@ -410,7 +410,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%ED%81%AC%EB%A6%AC</t>
   </si>
   <si>
-    <t>289조 7848억 8722만</t>
+    <t>291조 427억 7174만</t>
   </si>
   <si>
     <t>13</t>
@@ -422,7 +422,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%EB%84%A4%EC%A8%A9</t>
   </si>
   <si>
-    <t>284조 5621억 6052만</t>
+    <t>287조 4087억 5796만</t>
   </si>
   <si>
     <t>14</t>
@@ -437,7 +437,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>254조 8133억 6457만</t>
+    <t>255조 2513억 2505만</t>
   </si>
   <si>
     <t>15</t>
@@ -449,7 +449,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%85%8B%EC%A7%B8</t>
   </si>
   <si>
-    <t>186조 7701억 3305만</t>
+    <t>199조 1954억 8586만</t>
   </si>
   <si>
     <t>16</t>
@@ -488,7 +488,7 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>151조 2738억 4220만</t>
+    <t>152조 1480억 9079만</t>
   </si>
   <si>
     <t>19</t>
@@ -509,16 +509,31 @@
     <t>116조 7764억 2703만</t>
   </si>
   <si>
+    <t>냐락뀨리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%80%A8%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>104조 9072억 7456만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>Cerberus</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Cerberus</t>
   </si>
   <si>
-    <t>102조 9651억 6559만</t>
-  </si>
-  <si>
-    <t>21</t>
+    <t>103조 1944억 1367만</t>
+  </si>
+  <si>
+    <t>22</t>
   </si>
   <si>
     <t>삼양일짱</t>
@@ -527,24 +542,9 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EC%96%91%EC%9D%BC%EC%A7%B1</t>
   </si>
   <si>
-    <t>104</t>
-  </si>
-  <si>
     <t>101조 3977억 9940만</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>냐락뀨리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%80%A8%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>100조 5712억 8500만</t>
-  </si>
-  <si>
     <t>23</t>
   </si>
   <si>
@@ -554,7 +554,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%A7%80%EC%97%B0</t>
   </si>
   <si>
-    <t>100조 2429억 4818만</t>
+    <t>100조 4208억 8455만</t>
   </si>
   <si>
     <t>24</t>
@@ -569,7 +569,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>80조 592억 7105만</t>
+    <t>80조 2495억 315만</t>
   </si>
   <si>
     <t>이강민둥이</t>
@@ -599,7 +599,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EB%A0%88%EC%8F%98</t>
   </si>
   <si>
-    <t>45조 6552억 9994만</t>
+    <t>46조 737억 621만</t>
   </si>
   <si>
     <t>세정린</t>
@@ -620,7 +620,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B1%84%ED%9D%AC</t>
   </si>
   <si>
-    <t>34조 1931억 3448만</t>
+    <t>35조 2281억 5841만</t>
   </si>
   <si>
     <t>30</t>
@@ -632,7 +632,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B0%EB%8C%80%EA%B3%A4%EC%A4%84%EB%B0%95%EC%9D%B4</t>
   </si>
   <si>
-    <t>25조 4437억 8140만</t>
+    <t>25조 5321억 5285만</t>
   </si>
   <si>
     <t>스타냥이</t>
@@ -659,7 +659,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>1423조 266억 5967만</t>
+    <t>1946조 6213억 5027만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -677,7 +677,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
   </si>
   <si>
-    <t>841조 116억 1387만</t>
+    <t>962조 3461억 8276만</t>
   </si>
   <si>
     <t>빌런투킬</t>
@@ -686,7 +686,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
   </si>
   <si>
-    <t>822조 2645억 5459만</t>
+    <t>863조 4880억 8534만</t>
   </si>
   <si>
     <t>스타뎀</t>
@@ -713,7 +713,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
   </si>
   <si>
-    <t>133조 7562억 3908만</t>
+    <t>133조 9835억 1204만</t>
   </si>
   <si>
     <t>단풍노비</t>
@@ -740,7 +740,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
   </si>
   <si>
-    <t>113조 6898억 452만</t>
+    <t>124조 1249억 6059만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -752,13 +752,22 @@
     <t>76조 9998억 392만</t>
   </si>
   <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>70조 6447억 9453만</t>
+  </si>
+  <si>
     <t>꽃을든남자</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>66조 6902억 3016만</t>
+    <t>69조 2571억 2455만</t>
   </si>
   <si>
     <t>하후돈</t>
@@ -767,16 +776,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>63조 5620억 9620만</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>60조 5040억 5192만</t>
+    <t>65조 7023억 3999만</t>
   </si>
   <si>
     <t>POSCO</t>
@@ -806,7 +806,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
   </si>
   <si>
-    <t>34조 9644억 1726만</t>
+    <t>35조 532억 9817만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -824,7 +824,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>32조 9227억 9695만</t>
+    <t>33조 856억 7988만</t>
   </si>
   <si>
     <t>두근푸근연근</t>
@@ -842,7 +842,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>28조 9628억 4583만</t>
+    <t>29조 1275억 1565만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
@@ -851,6 +851,15 @@
     <t>26조 735억 6034만</t>
   </si>
   <si>
+    <t>포뇨야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
+  </si>
+  <si>
+    <t>25조 4912억 9969만</t>
+  </si>
+  <si>
     <t>울힝</t>
   </si>
   <si>
@@ -878,15 +887,6 @@
     <t>22조 162억 9023만</t>
   </si>
   <si>
-    <t>포뇨야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
-  </si>
-  <si>
-    <t>19조 3934억 1559만</t>
-  </si>
-  <si>
     <t>몽호</t>
   </si>
   <si>
@@ -905,19 +905,16 @@
     <t>9조 4979억 5390만</t>
   </si>
   <si>
-    <t>26샤넬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EC%83%A4%EB%84%AC</t>
+    <t>26순혁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EC%88%9C%ED%98%81</t>
   </si>
   <si>
     <t>111</t>
   </si>
   <si>
-    <t>1경 5997조 4500억 56만</t>
-  </si>
-  <si>
-    <t>살뽀시</t>
+    <t>1경 6443조 1834억 7428만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
@@ -926,7 +923,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>2364조 3434억 4144만</t>
+    <t>2502조 9826억 7967만</t>
   </si>
   <si>
     <t>26상탗</t>
@@ -935,7 +932,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EC%83%81%ED%83%97</t>
   </si>
   <si>
-    <t>1300조 8953억 6300만</t>
+    <t>1301조 7924억 7329만</t>
   </si>
   <si>
     <t>뇌쉬</t>
@@ -944,7 +941,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
   </si>
   <si>
-    <t>455조 8742억 5793만</t>
+    <t>462조 3946억 8834만</t>
   </si>
   <si>
     <t>찐빵은</t>
@@ -962,7 +959,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
   </si>
   <si>
-    <t>353조 6581억 1141만</t>
+    <t>372조 867억 9160만</t>
   </si>
   <si>
     <t>26들박</t>
@@ -971,16 +968,16 @@
     <t>https://mgf.gg/contents/character.php?n=26%EB%93%A4%EB%B0%95</t>
   </si>
   <si>
-    <t>307조 2219억 5257만</t>
-  </si>
-  <si>
-    <t>26샤서</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EC%83%A4%EC%84%9C</t>
-  </si>
-  <si>
-    <t>235조 9681억 302만</t>
+    <t>310조 6004억 7184만</t>
+  </si>
+  <si>
+    <t>서예슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>255조 8017억 1535만</t>
   </si>
   <si>
     <t>26빵은</t>
@@ -989,7 +986,16 @@
     <t>https://mgf.gg/contents/character.php?n=26%EB%B9%B5%EC%9D%80</t>
   </si>
   <si>
-    <t>200조 264억 2750만</t>
+    <t>222조 1071억 7012만</t>
+  </si>
+  <si>
+    <t>임승민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>124조 712억 140만</t>
   </si>
   <si>
     <t>26밍밍</t>
@@ -1001,22 +1007,13 @@
     <t>119조 856억 3291만</t>
   </si>
   <si>
-    <t>임승민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>118조 5973억 1454만</t>
-  </si>
-  <si>
     <t>26횟집</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=26%ED%9A%9F%EC%A7%91</t>
   </si>
   <si>
-    <t>96조 2143억 4641만</t>
+    <t>96조 9899억 6229만</t>
   </si>
   <si>
     <t>뻔수니</t>
@@ -1025,7 +1022,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
   </si>
   <si>
-    <t>54조 4054억 8639만</t>
+    <t>56조 557억 2565만</t>
   </si>
   <si>
     <t>얼음깨먹기</t>
@@ -1070,7 +1067,16 @@
     <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
   </si>
   <si>
-    <t>17조 8598억 7194만</t>
+    <t>17조 9480억 6864만</t>
+  </si>
+  <si>
+    <t>아모르파티퀘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
+  </si>
+  <si>
+    <t>17조 1585억 8689만</t>
   </si>
   <si>
     <t>뻐늬</t>
@@ -1079,7 +1085,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
   </si>
   <si>
-    <t>16조 1737억 7347만</t>
+    <t>16조 1989억 14만</t>
   </si>
   <si>
     <t>26조선</t>
@@ -1100,15 +1106,6 @@
     <t>12조 6004억 5926만</t>
   </si>
   <si>
-    <t>아모르파티퀘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
-  </si>
-  <si>
-    <t>12조 4052억 1410만</t>
-  </si>
-  <si>
     <t>최씨용</t>
   </si>
   <si>
@@ -1124,7 +1121,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
   </si>
   <si>
-    <t>8조 4686억 2378만</t>
+    <t>8조 8839억 1009만</t>
   </si>
   <si>
     <t>뿜삐</t>
@@ -1136,7 +1133,7 @@
     <t>100</t>
   </si>
   <si>
-    <t>7조 7751억 4203만</t>
+    <t>8조 3343억 8600만</t>
   </si>
   <si>
     <t>예라미</t>
@@ -1145,7 +1142,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
   </si>
   <si>
-    <t>6조 5224억 1405만</t>
+    <t>6조 5507억 9718만</t>
   </si>
   <si>
     <t>귬스파파</t>
@@ -1163,556 +1160,541 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%98%81%ED%9D%AC%EB%A9%88%EB%AD%84%EB%AF%B8</t>
   </si>
   <si>
-    <t>5조 1256억 509만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EC%9B%8C%EC%BB%A4</t>
+    <t>5조 2058억 6573만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EA%B8%B0%EC%9A%94%EB%B0%8B</t>
+  </si>
+  <si>
+    <t>1경 3416조 6921억 5835만</t>
+  </si>
+  <si>
+    <t>일월마녀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%EC%9B%94%EB%A7%88%EB%85%80</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>4378조 604억 9661만</t>
+  </si>
+  <si>
+    <t>난풍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%ED%92%8D</t>
+  </si>
+  <si>
+    <t>1154조 7823억 2893만</t>
+  </si>
+  <si>
+    <t>로드숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%93%9C%EC%88%8D</t>
+  </si>
+  <si>
+    <t>764조 3776억 8930만</t>
+  </si>
+  <si>
+    <t>누짜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EC%A7%9C</t>
+  </si>
+  <si>
+    <t>624조 598억 3395만</t>
+  </si>
+  <si>
+    <t>송곧</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EA%B3%A7</t>
+  </si>
+  <si>
+    <t>536조 1566억 7259만</t>
+  </si>
+  <si>
+    <t>똥으리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EC%9C%BC%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>246조 1144억 5306만</t>
+  </si>
+  <si>
+    <t>다이사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9D%B4%EC%82%AC</t>
+  </si>
+  <si>
+    <t>171조 9276억 4935만</t>
+  </si>
+  <si>
+    <t>피몽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EB%AA%BD</t>
+  </si>
+  <si>
+    <t>131조 6403억 8429만</t>
+  </si>
+  <si>
+    <t>진짜지존법사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%A7%9C%EC%A7%80%EC%A1%B4%EB%B2%95%EC%82%AC</t>
+  </si>
+  <si>
+    <t>109조 2489억 3589만</t>
+  </si>
+  <si>
+    <t>원순철</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%88%9C%EC%B2%A0</t>
+  </si>
+  <si>
+    <t>43조 9652억 6611만</t>
+  </si>
+  <si>
+    <t>ADELL</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=ADELL</t>
+  </si>
+  <si>
+    <t>37조 1257억 1386만</t>
+  </si>
+  <si>
+    <t>쿠소가키키</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%86%8C%EA%B0%80%ED%82%A4%ED%82%A4</t>
+  </si>
+  <si>
+    <t>18조 706억 7816만</t>
+  </si>
+  <si>
+    <t>태켱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BC%B1</t>
+  </si>
+  <si>
+    <t>13조 7240억 3347만</t>
+  </si>
+  <si>
+    <t>왓쳐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%93%EC%B3%90</t>
+  </si>
+  <si>
+    <t>12조 4928억 180만</t>
+  </si>
+  <si>
+    <t>유디티기찬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%94%94%ED%8B%B0%EA%B8%B0%EC%B0%AC</t>
+  </si>
+  <si>
+    <t>11조 3222억 4934만</t>
+  </si>
+  <si>
+    <t>박미쯔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%AF%B8%EC%AF%94</t>
+  </si>
+  <si>
+    <t>11조 396억 3541만</t>
+  </si>
+  <si>
+    <t>끽코</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%BD%94</t>
+  </si>
+  <si>
+    <t>10조 5748억 5807만</t>
+  </si>
+  <si>
+    <t>강띵띵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%9D%B5%EB%9D%B5</t>
+  </si>
+  <si>
+    <t>8조 2123억 8705만</t>
+  </si>
+  <si>
+    <t>악전</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%A0%84</t>
+  </si>
+  <si>
+    <t>6조 6792억 8468만</t>
+  </si>
+  <si>
+    <t>키우는건질색</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9A%B0%EB%8A%94%EA%B1%B4%EC%A7%88%EC%83%89</t>
+  </si>
+  <si>
+    <t>6조 4672억 7973만</t>
+  </si>
+  <si>
+    <t>후아멀로하냐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%95%84%EB%A9%80%EB%A1%9C%ED%95%98%EB%83%90</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>5조 8473억 6277만</t>
+  </si>
+  <si>
+    <t>햄쓱이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%96%84%EC%93%B1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>5조 4672억 9243만</t>
+  </si>
+  <si>
+    <t>SingA</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=SingA</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>4조 8708억 1278만</t>
+  </si>
+  <si>
+    <t>술취한호랑이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EC%B7%A8%ED%95%9C%ED%98%B8%EB%9E%91%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>4조 4630억 8275만</t>
+  </si>
+  <si>
+    <t>한Poll</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9CPoll</t>
+  </si>
+  <si>
+    <t>3조 9956억 1684만</t>
+  </si>
+  <si>
+    <t>수년</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%85%84</t>
+  </si>
+  <si>
+    <t>3조 8612억 4341만</t>
+  </si>
+  <si>
+    <t>김치왕뚜껑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%99%95%EB%9A%9C%EA%BB%91</t>
+  </si>
+  <si>
+    <t>3조 4955억 2414만</t>
+  </si>
+  <si>
+    <t>쿠쏘야로로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%8F%98%EC%95%BC%EB%A1%9C%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>2조 3439억 9014만</t>
+  </si>
+  <si>
+    <t>치즈왕뚜껑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%A6%88%EC%99%95%EB%9A%9C%EA%BB%91</t>
+  </si>
+  <si>
+    <t>2조 1538억 2144만</t>
+  </si>
+  <si>
+    <t>신궁쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%81%EC%A8%A9</t>
+  </si>
+  <si>
+    <t>8668조 7855억 1234만</t>
+  </si>
+  <si>
+    <t>싸뤽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
+  </si>
+  <si>
+    <t>7064조 1272억 3711만</t>
+  </si>
+  <si>
+    <t>실민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>1079조 207억 5639만</t>
+  </si>
+  <si>
+    <t>약한고등어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
+  </si>
+  <si>
+    <t>720조 4647억 4246만</t>
+  </si>
+  <si>
+    <t>민실</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%8B%A4</t>
+  </si>
+  <si>
+    <t>568조 5879억 7585만</t>
+  </si>
+  <si>
+    <t>앨삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EC%82%90</t>
+  </si>
+  <si>
+    <t>265조 7402억 6624만</t>
+  </si>
+  <si>
+    <t>문디르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>188조 2968억 5490만</t>
+  </si>
+  <si>
+    <t>항상밝은하루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AD%EC%83%81%EB%B0%9D%EC%9D%80%ED%95%98%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>174조 1834억 1713만</t>
+  </si>
+  <si>
+    <t>비트츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%ED%8A%B8%EC%B8%84</t>
+  </si>
+  <si>
+    <t>124조 4229억 3053만</t>
+  </si>
+  <si>
+    <t>봉튜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%8A%9C</t>
+  </si>
+  <si>
+    <t>101조 5005억 6045만</t>
+  </si>
+  <si>
+    <t>월광사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%94%EA%B4%91%EC%82%AC</t>
+  </si>
+  <si>
+    <t>88조 8232억 3579만</t>
+  </si>
+  <si>
+    <t>공포의오함마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%8F%AC%EC%9D%98%EC%98%A4%ED%95%A8%EB%A7%88</t>
+  </si>
+  <si>
+    <t>59조 7852억 2884만</t>
+  </si>
+  <si>
+    <t>은달총</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%AC%EC%B4%9D</t>
+  </si>
+  <si>
+    <t>37조 9875억 239만</t>
+  </si>
+  <si>
+    <t>꽃나래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
+  </si>
+  <si>
+    <t>37조 8956억 2896만</t>
+  </si>
+  <si>
+    <t>김대협</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8C%80%ED%98%91</t>
+  </si>
+  <si>
+    <t>22조 2718억 3445만</t>
+  </si>
+  <si>
+    <t>땩콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>21조 7998억 5419만</t>
+  </si>
+  <si>
+    <t>에망</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
+  </si>
+  <si>
+    <t>11조 7922억 1619만</t>
+  </si>
+  <si>
+    <t>낭만만듀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%EB%A7%8C%EB%93%80</t>
+  </si>
+  <si>
+    <t>10조 3682억 9319만</t>
+  </si>
+  <si>
+    <t>봄녘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EB%85%98</t>
+  </si>
+  <si>
+    <t>8조 5071억 3693만</t>
+  </si>
+  <si>
+    <t>다송이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>7조 6214억 2565만</t>
+  </si>
+  <si>
+    <t>빠나딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EB%94%98</t>
+  </si>
+  <si>
+    <t>6조 8464억 1602만</t>
+  </si>
+  <si>
+    <t>봉합불가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>5조 6976억 9508만</t>
+  </si>
+  <si>
+    <t>양카오너</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%B9%B4%EC%98%A4%EB%84%88</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>2조 4997억 7676만</t>
+  </si>
+  <si>
+    <t>강한고등어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
+  </si>
+  <si>
+    <t>2조 4534억 4841만</t>
+  </si>
+  <si>
+    <t>돌쇠영만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
+  </si>
+  <si>
+    <t>1조 77억 4734만</t>
+  </si>
+  <si>
+    <t>용광사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EA%B4%91%EC%82%AC</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>5941억 677만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
+  </si>
+  <si>
+    <t>5446억 9840만</t>
+  </si>
+  <si>
+    <t>비어치킨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%96%B4%EC%B9%98%ED%82%A8</t>
   </si>
   <si>
     <t>94</t>
   </si>
   <si>
-    <t>6929억 5612만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EA%B8%B0%EC%9A%94%EB%B0%8B</t>
-  </si>
-  <si>
-    <t>1경 3416조 6921억 5835만</t>
-  </si>
-  <si>
-    <t>일월마녀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%EC%9B%94%EB%A7%88%EB%85%80</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>4378조 604억 9661만</t>
-  </si>
-  <si>
-    <t>난풍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%ED%92%8D</t>
-  </si>
-  <si>
-    <t>1086조 8133억 5735만</t>
-  </si>
-  <si>
-    <t>로드숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%93%9C%EC%88%8D</t>
-  </si>
-  <si>
-    <t>764조 3776억 8930만</t>
-  </si>
-  <si>
-    <t>누짜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EC%A7%9C</t>
-  </si>
-  <si>
-    <t>624조 598억 3395만</t>
-  </si>
-  <si>
-    <t>송곧</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EA%B3%A7</t>
-  </si>
-  <si>
-    <t>468조 6207억 8352만</t>
-  </si>
-  <si>
-    <t>똥으리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EC%9C%BC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>245조 6657억 977만</t>
-  </si>
-  <si>
-    <t>다이사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9D%B4%EC%82%AC</t>
-  </si>
-  <si>
-    <t>165조 9845억 4310만</t>
-  </si>
-  <si>
-    <t>피몽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EB%AA%BD</t>
-  </si>
-  <si>
-    <t>131조 3358억 1662만</t>
-  </si>
-  <si>
-    <t>진짜지존법사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%A7%9C%EC%A7%80%EC%A1%B4%EB%B2%95%EC%82%AC</t>
-  </si>
-  <si>
-    <t>103조 4606억 3241만</t>
-  </si>
-  <si>
-    <t>원순철</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%88%9C%EC%B2%A0</t>
-  </si>
-  <si>
-    <t>43조 9652억 6611만</t>
-  </si>
-  <si>
-    <t>ADELL</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=ADELL</t>
-  </si>
-  <si>
-    <t>35조 9805억 9383만</t>
-  </si>
-  <si>
-    <t>쿠소가키키</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%86%8C%EA%B0%80%ED%82%A4%ED%82%A4</t>
-  </si>
-  <si>
-    <t>14조 9838억 6878만</t>
-  </si>
-  <si>
-    <t>태켱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BC%B1</t>
-  </si>
-  <si>
-    <t>13조 3344억 1444만</t>
-  </si>
-  <si>
-    <t>왓쳐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%93%EC%B3%90</t>
-  </si>
-  <si>
-    <t>12조 3951억 3587만</t>
-  </si>
-  <si>
-    <t>유디티기찬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%94%94%ED%8B%B0%EA%B8%B0%EC%B0%AC</t>
-  </si>
-  <si>
-    <t>11조 3222억 4934만</t>
-  </si>
-  <si>
-    <t>박미쯔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%AF%B8%EC%AF%94</t>
-  </si>
-  <si>
-    <t>11조 396억 3541만</t>
-  </si>
-  <si>
-    <t>끽코</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%BD%94</t>
-  </si>
-  <si>
-    <t>10조 5748억 5807만</t>
-  </si>
-  <si>
-    <t>강띵띵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%9D%B5%EB%9D%B5</t>
-  </si>
-  <si>
-    <t>8조 2123억 8705만</t>
-  </si>
-  <si>
-    <t>악전</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%A0%84</t>
-  </si>
-  <si>
-    <t>6조 1844억 1816만</t>
-  </si>
-  <si>
-    <t>후아멀로하냐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%95%84%EB%A9%80%EB%A1%9C%ED%95%98%EB%83%90</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>5조 8473억 6277만</t>
-  </si>
-  <si>
-    <t>햄쓱이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%96%84%EC%93%B1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>5조 4672억 9243만</t>
-  </si>
-  <si>
-    <t>SingA</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=SingA</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>4조 7618억 8122만</t>
-  </si>
-  <si>
-    <t>술취한호랑이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EC%B7%A8%ED%95%9C%ED%98%B8%EB%9E%91%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>4조 4630억 8275만</t>
-  </si>
-  <si>
-    <t>한Poll</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9CPoll</t>
-  </si>
-  <si>
-    <t>3조 9616억 4440만</t>
-  </si>
-  <si>
-    <t>수년</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%85%84</t>
-  </si>
-  <si>
-    <t>3조 8581억 5699만</t>
-  </si>
-  <si>
-    <t>김치왕뚜껑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%99%95%EB%9A%9C%EA%BB%91</t>
-  </si>
-  <si>
-    <t>3조 4955억 2414만</t>
-  </si>
-  <si>
-    <t>올바른생활</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%AC%EB%B0%94%EB%A5%B8%EC%83%9D%ED%99%9C</t>
-  </si>
-  <si>
-    <t>2조 3091억 9295만</t>
-  </si>
-  <si>
-    <t>치즈왕뚜껑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%A6%88%EC%99%95%EB%9A%9C%EA%BB%91</t>
-  </si>
-  <si>
-    <t>2조 693억 5496만</t>
-  </si>
-  <si>
-    <t>쿠쏘야로로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%8F%98%EC%95%BC%EB%A1%9C%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>1조 6595억 7116만</t>
-  </si>
-  <si>
-    <t>신궁쨩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%81%EC%A8%A9</t>
-  </si>
-  <si>
-    <t>8668조 7855억 1234만</t>
-  </si>
-  <si>
-    <t>싸뤽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
-  </si>
-  <si>
-    <t>7064조 1272억 3711만</t>
-  </si>
-  <si>
-    <t>실민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>1079조 207억 5639만</t>
-  </si>
-  <si>
-    <t>약한고등어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
-  </si>
-  <si>
-    <t>720조 4647억 4246만</t>
-  </si>
-  <si>
-    <t>민실</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%8B%A4</t>
-  </si>
-  <si>
-    <t>505조 6260억 8801만</t>
-  </si>
-  <si>
-    <t>앨삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EC%82%90</t>
-  </si>
-  <si>
-    <t>238조 8293억 3893만</t>
-  </si>
-  <si>
-    <t>문디르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>174조 3495억 1503만</t>
-  </si>
-  <si>
-    <t>항상밝은하루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AD%EC%83%81%EB%B0%9D%EC%9D%80%ED%95%98%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>139조 5654억 2106만</t>
-  </si>
-  <si>
-    <t>비트츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%ED%8A%B8%EC%B8%84</t>
-  </si>
-  <si>
-    <t>124조 4229억 3053만</t>
-  </si>
-  <si>
-    <t>봉튜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%8A%9C</t>
-  </si>
-  <si>
-    <t>89조 4233억 30만</t>
-  </si>
-  <si>
-    <t>월광사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%94%EA%B4%91%EC%82%AC</t>
-  </si>
-  <si>
-    <t>88조 8232억 3579만</t>
-  </si>
-  <si>
-    <t>공포의오함마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%8F%AC%EC%9D%98%EC%98%A4%ED%95%A8%EB%A7%88</t>
-  </si>
-  <si>
-    <t>59조 7852억 2884만</t>
-  </si>
-  <si>
-    <t>날강도팔라딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EA%B0%95%EB%8F%84%ED%8C%94%EB%9D%BC%EB%94%98</t>
-  </si>
-  <si>
-    <t>41조 2006억 9971만</t>
-  </si>
-  <si>
-    <t>은달총</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%AC%EC%B4%9D</t>
-  </si>
-  <si>
-    <t>37조 9875억 239만</t>
-  </si>
-  <si>
-    <t>꽃나래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
-  </si>
-  <si>
-    <t>37조 8517억 1089만</t>
-  </si>
-  <si>
-    <t>김대협</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8C%80%ED%98%91</t>
-  </si>
-  <si>
-    <t>21조 6036억 5513만</t>
-  </si>
-  <si>
-    <t>땩콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>17조 9771억 1515만</t>
-  </si>
-  <si>
-    <t>에망</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
-  </si>
-  <si>
-    <t>11조 6961억 5084만</t>
-  </si>
-  <si>
-    <t>낭만만듀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%EB%A7%8C%EB%93%80</t>
-  </si>
-  <si>
-    <t>10조 1220억 3937만</t>
-  </si>
-  <si>
-    <t>봄녘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EB%85%98</t>
-  </si>
-  <si>
-    <t>8조 5071억 3693만</t>
-  </si>
-  <si>
-    <t>다송이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>7조 3029억 1297만</t>
-  </si>
-  <si>
-    <t>빠나딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EB%94%98</t>
-  </si>
-  <si>
-    <t>6조 8464억 1602만</t>
-  </si>
-  <si>
-    <t>봉합불가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>5조 6767억 6686만</t>
-  </si>
-  <si>
-    <t>양카오너</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%B9%B4%EC%98%A4%EB%84%88</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>2조 1902억 4635만</t>
-  </si>
-  <si>
-    <t>강한고등어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
-  </si>
-  <si>
-    <t>2조 580억 3912만</t>
-  </si>
-  <si>
-    <t>돌쇠영만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
-  </si>
-  <si>
-    <t>9591억 6321만</t>
-  </si>
-  <si>
-    <t>용광사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EA%B4%91%EC%82%AC</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>5941억 677만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
-  </si>
-  <si>
-    <t>5446억 9840만</t>
-  </si>
-  <si>
-    <t>비어치킨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%96%B4%EC%B9%98%ED%82%A8</t>
-  </si>
-  <si>
-    <t>3071억 3981만</t>
+    <t>3653억 5893만</t>
   </si>
 </sst>
 </file>
@@ -2597,25 +2579,25 @@
         <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2626,28 +2608,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2658,25 +2640,25 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>114</v>
@@ -2708,7 +2690,7 @@
         <v>92</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>118</v>
@@ -2740,7 +2722,7 @@
         <v>122</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>123</v>
@@ -2772,7 +2754,7 @@
         <v>86</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>127</v>
@@ -2801,10 +2783,10 @@
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>131</v>
@@ -3025,13 +3007,13 @@
         <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3042,25 +3024,25 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>167</v>
@@ -3089,10 +3071,10 @@
         <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>171</v>
@@ -3124,7 +3106,7 @@
         <v>97</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>175</v>
@@ -3153,7 +3135,7 @@
         <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>179</v>
@@ -3185,7 +3167,7 @@
         <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>179</v>
@@ -3252,7 +3234,7 @@
         <v>97</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>190</v>
@@ -3313,7 +3295,7 @@
         <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>179</v>
@@ -3462,7 +3444,7 @@
         <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>71</v>
@@ -3590,7 +3572,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>87</v>
@@ -3657,7 +3639,7 @@
         <v>92</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>222</v>
@@ -3671,7 +3653,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>223</v>
@@ -3689,7 +3671,7 @@
         <v>92</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>225</v>
@@ -3703,7 +3685,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>226</v>
@@ -3718,7 +3700,7 @@
         <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>135</v>
@@ -3782,7 +3764,7 @@
         <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>135</v>
@@ -3814,7 +3796,7 @@
         <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>179</v>
@@ -3846,7 +3828,7 @@
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>135</v>
@@ -3878,10 +3860,10 @@
         <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>243</v>
@@ -3910,10 +3892,10 @@
         <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>246</v>
@@ -3942,10 +3924,10 @@
         <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>249</v>
@@ -3977,7 +3959,7 @@
         <v>92</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>252</v>
@@ -4006,7 +3988,7 @@
         <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>255</v>
@@ -4070,10 +4052,10 @@
         <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>262</v>
@@ -4087,7 +4069,7 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>263</v>
@@ -4166,7 +4148,7 @@
         <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>179</v>
@@ -4195,7 +4177,7 @@
         <v>272</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>81</v>
@@ -4233,7 +4215,7 @@
         <v>81</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>276</v>
@@ -4262,7 +4244,7 @@
         <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>158</v>
@@ -4294,10 +4276,10 @@
         <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>282</v>
@@ -4326,7 +4308,7 @@
         <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>179</v>
@@ -4390,7 +4372,7 @@
         <v>69</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>158</v>
@@ -4442,7 +4424,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4451,7 +4433,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4527,25 +4509,25 @@
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>297</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>70</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4559,25 +4541,25 @@
         <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>301</v>
-      </c>
       <c r="F4" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4591,13 +4573,13 @@
         <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>69</v>
@@ -4606,10 +4588,10 @@
         <v>122</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4623,25 +4605,25 @@
         <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="F6" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4655,13 +4637,13 @@
         <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>69</v>
@@ -4670,10 +4652,10 @@
         <v>92</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4687,13 +4669,13 @@
         <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>313</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>69</v>
@@ -4702,10 +4684,10 @@
         <v>92</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4716,16 +4698,16 @@
         <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>316</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>69</v>
@@ -4734,10 +4716,10 @@
         <v>81</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4748,16 +4730,16 @@
         <v>32</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>69</v>
@@ -4766,10 +4748,10 @@
         <v>81</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4783,25 +4765,25 @@
         <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>323</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4815,25 +4797,25 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>326</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4847,13 +4829,13 @@
         <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>328</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>69</v>
@@ -4862,10 +4844,10 @@
         <v>86</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4879,25 +4861,25 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>331</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>179</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4911,13 +4893,13 @@
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>69</v>
@@ -4929,7 +4911,7 @@
         <v>179</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4943,25 +4925,25 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>337</v>
-      </c>
       <c r="F16" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>179</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4975,25 +4957,25 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>340</v>
-      </c>
       <c r="F17" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5007,25 +4989,25 @@
         <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>343</v>
-      </c>
       <c r="F18" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5039,13 +5021,13 @@
         <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>346</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>69</v>
@@ -5057,7 +5039,7 @@
         <v>179</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5071,25 +5053,25 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>349</v>
-      </c>
       <c r="F20" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5103,25 +5085,25 @@
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>352</v>
-      </c>
       <c r="F21" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5132,28 +5114,28 @@
         <v>32</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>356</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5167,25 +5149,25 @@
         <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>359</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5199,13 +5181,13 @@
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>69</v>
@@ -5217,7 +5199,7 @@
         <v>255</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5231,13 +5213,13 @@
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>364</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>69</v>
@@ -5249,7 +5231,7 @@
         <v>255</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5263,13 +5245,13 @@
         <v>35</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>69</v>
@@ -5278,10 +5260,10 @@
         <v>92</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5295,13 +5277,13 @@
         <v>44</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>69</v>
@@ -5313,7 +5295,7 @@
         <v>255</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5327,13 +5309,13 @@
         <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>69</v>
@@ -5342,10 +5324,10 @@
         <v>81</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>368</v>
+        <v>255</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5359,13 +5341,13 @@
         <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>69</v>
@@ -5377,46 +5359,14 @@
         <v>255</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J29"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -5446,7 +5396,6 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5513,10 +5462,10 @@
         <v>47</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>81</v>
@@ -5525,7 +5474,7 @@
         <v>294</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5539,25 +5488,25 @@
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5571,25 +5520,25 @@
         <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5603,13 +5552,13 @@
         <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>69</v>
@@ -5618,10 +5567,10 @@
         <v>70</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5635,13 +5584,13 @@
         <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>69</v>
@@ -5653,7 +5602,7 @@
         <v>135</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5667,13 +5616,13 @@
         <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>69</v>
@@ -5682,10 +5631,10 @@
         <v>81</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5699,25 +5648,25 @@
         <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5728,28 +5677,28 @@
         <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5760,16 +5709,16 @@
         <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>69</v>
@@ -5781,7 +5730,7 @@
         <v>135</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5795,13 +5744,13 @@
         <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>69</v>
@@ -5813,7 +5762,7 @@
         <v>158</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5827,25 +5776,25 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5859,13 +5808,13 @@
         <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>69</v>
@@ -5877,7 +5826,7 @@
         <v>255</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5891,25 +5840,25 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5923,13 +5872,13 @@
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>69</v>
@@ -5941,7 +5890,7 @@
         <v>255</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5955,25 +5904,25 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>179</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5987,13 +5936,13 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>69</v>
@@ -6005,7 +5954,7 @@
         <v>255</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6019,13 +5968,13 @@
         <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>69</v>
@@ -6037,7 +5986,7 @@
         <v>255</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6051,13 +6000,13 @@
         <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>69</v>
@@ -6069,7 +6018,7 @@
         <v>255</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6083,13 +6032,13 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>69</v>
@@ -6101,7 +6050,7 @@
         <v>255</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6115,25 +6064,25 @@
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>255</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6144,28 +6093,28 @@
         <v>41</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>444</v>
+        <v>367</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6179,25 +6128,25 @@
         <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>368</v>
+        <v>443</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6211,25 +6160,25 @@
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>451</v>
+        <v>367</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6243,25 +6192,25 @@
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>368</v>
+        <v>450</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6275,25 +6224,25 @@
         <v>35</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>444</v>
+        <v>367</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6307,25 +6256,25 @@
         <v>44</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>368</v>
+        <v>443</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6339,25 +6288,25 @@
         <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6371,25 +6320,25 @@
         <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>444</v>
+        <v>255</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6403,25 +6352,25 @@
         <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6435,25 +6384,25 @@
         <v>198</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6499,7 +6448,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -6552,13 +6501,13 @@
         <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>69</v>
@@ -6570,7 +6519,7 @@
         <v>294</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6584,13 +6533,13 @@
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>69</v>
@@ -6599,10 +6548,10 @@
         <v>70</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6616,25 +6565,25 @@
         <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6648,25 +6597,25 @@
         <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6680,13 +6629,13 @@
         <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>69</v>
@@ -6695,10 +6644,10 @@
         <v>92</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6712,13 +6661,13 @@
         <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>69</v>
@@ -6727,10 +6676,10 @@
         <v>97</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6744,13 +6693,13 @@
         <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>69</v>
@@ -6762,7 +6711,7 @@
         <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6773,16 +6722,16 @@
         <v>48</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>69</v>
@@ -6794,7 +6743,7 @@
         <v>179</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6805,16 +6754,16 @@
         <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>69</v>
@@ -6823,10 +6772,10 @@
         <v>70</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6840,25 +6789,25 @@
         <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6872,13 +6821,13 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>69</v>
@@ -6890,7 +6839,7 @@
         <v>179</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6904,25 +6853,25 @@
         <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>179</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6936,25 +6885,25 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6968,25 +6917,25 @@
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>157</v>
+        <v>113</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>179</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7000,25 +6949,25 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>179</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7032,25 +6981,25 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>158</v>
+        <v>255</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7064,25 +7013,25 @@
         <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>255</v>
+        <v>367</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7096,25 +7045,25 @@
         <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7128,25 +7077,25 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7160,25 +7109,25 @@
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7189,28 +7138,28 @@
         <v>48</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7224,13 +7173,13 @@
         <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>69</v>
@@ -7239,10 +7188,10 @@
         <v>92</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>368</v>
+        <v>443</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7256,25 +7205,25 @@
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>444</v>
+        <v>538</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7288,25 +7237,25 @@
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>545</v>
+        <v>443</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7320,25 +7269,25 @@
         <v>35</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>157</v>
+        <v>92</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>451</v>
+        <v>538</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7352,25 +7301,25 @@
         <v>44</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7384,25 +7333,25 @@
         <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>553</v>
+        <v>57</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>553</v>
+        <v>57</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>70</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7416,64 +7365,32 @@
         <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>57</v>
+        <v>552</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>57</v>
+        <v>552</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J29"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -7503,7 +7420,6 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/셀린느/셀린느_mgf_matched_5_guilds.xlsx
+++ b/reports/셀린느/셀린느_mgf_matched_5_guilds.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">LUXURY!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">냐락!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">셀린느!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">이콩!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">이콩!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">호러!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="561">
   <si>
     <t>guild_name</t>
   </si>
@@ -113,495 +113,501 @@
     <t>Scania 2</t>
   </si>
   <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>2경 302조 8354억 4885만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.04.11</t>
+  </si>
+  <si>
+    <t>LUXURY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
+  </si>
+  <si>
+    <t>Scania 16</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>2경 2185조 8183억 1617만</t>
+  </si>
+  <si>
+    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
+  </si>
+  <si>
+    <t>살뽀시</t>
+  </si>
+  <si>
+    <t>호러</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%98%B8%EB%9F%AC</t>
+  </si>
+  <si>
+    <t>Scania 10</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>2경 1593조 2154억 9496만</t>
+  </si>
+  <si>
+    <t>오래 하실분들 환영입니다</t>
+  </si>
+  <si>
+    <t>애기요밋</t>
+  </si>
+  <si>
+    <t>이콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>Scania 28</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>4위</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>28명</t>
+  </si>
+  <si>
+    <t>1경 9137조 3448억 6787만</t>
+  </si>
+  <si>
+    <t>가입문의 - 요쯔</t>
+  </si>
+  <si>
+    <t>요쯔</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>냐락불곰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%B6%88%EA%B3%B0</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>1경 2229조 7494억 2484만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>냐락오리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%98%A4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>2162조 4673억 382만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>썬콜법사님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%AC%EB%8B%98</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>2149조 1176억 4861만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>냐락겅듀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EA%B2%85%EB%93%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>1982조 8748억 2848만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>벽서</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%BD%EC%84%9C</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>1389조 2663억 3276만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>냐락바람</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%B0%94%EB%9E%8C</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>875조 7755억 8766만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%A7%90</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>827조 5226억 4948만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>닭도리도리탕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AD%EB%8F%84%EB%A6%AC%EB%8F%84%EB%A6%AC%ED%83%95</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>742조 6263억 3641만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>이대팔가르마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8C%80%ED%8C%94%EA%B0%80%EB%A5%B4%EB%A7%88</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>739조 9535억 2604만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>눈꽃체리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%88%EA%BD%83%EC%B2%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>464조 9749억 4990만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>망치두고튀어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%91%90%EA%B3%A0%ED%8A%80%EC%96%B4</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>391조 5083억 9813만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>냐락크리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%ED%81%AC%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>291조 427억 7174만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>떠네쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%EB%84%A4%EC%A8%A9</t>
+  </si>
+  <si>
+    <t>287조 4087억 5796만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>왕푸맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%ED%91%B8%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>274조 9324억 390만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>냐락셋째</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%85%8B%EC%A7%B8</t>
+  </si>
+  <si>
+    <t>200조 1259억 9854만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>냐락린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>188조 9953억 4686만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>냐락쿠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%BF%A0</t>
+  </si>
+  <si>
+    <t>168조 2748억 1327만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>쀼움</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%80%BC%EC%9B%80</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>152조 1480억 9079만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>삼양일짱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EC%96%91%EC%9D%BC%EC%A7%B1</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>133조 5577억 192만</t>
+  </si>
+  <si>
+    <t>샤미다미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EB%AF%B8%EB%8B%A4%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>116조 7764억 2703만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>냐락뀨리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%80%A8%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>104조 9239억 1201만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>안지연</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%A7%80%EC%97%B0</t>
+  </si>
+  <si>
+    <t>103조 5157억 8876만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Cerberus</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Cerberus</t>
+  </si>
+  <si>
+    <t>103조 4463억 3620만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>와칸다검식이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%80%EC%B9%B8%EB%8B%A4%EA%B2%80%EC%8B%9D%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>80조 2495억 315만</t>
+  </si>
+  <si>
+    <t>이강민둥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B0%95%EB%AF%BC%EB%91%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>67조 223억 9864만</t>
+  </si>
+  <si>
+    <t>히들</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EB%93%A4</t>
+  </si>
+  <si>
+    <t>65조 1068억 8052만</t>
+  </si>
+  <si>
+    <t>국레쏘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EB%A0%88%EC%8F%98</t>
+  </si>
+  <si>
+    <t>50조 896억 2626만</t>
+  </si>
+  <si>
     <t>28</t>
   </si>
   <si>
-    <t>2경 38조 753억 677만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>LUXURY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
-  </si>
-  <si>
-    <t>Scania 16</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>2경 2185조 8183억 1617만</t>
-  </si>
-  <si>
-    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
-  </si>
-  <si>
-    <t>살뽀시</t>
-  </si>
-  <si>
-    <t>호러</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%98%B8%EB%9F%AC</t>
-  </si>
-  <si>
-    <t>Scania 10</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>2경 1593조 2154억 9496만</t>
-  </si>
-  <si>
-    <t>오래 하실분들 환영입니다</t>
-  </si>
-  <si>
-    <t>애기요밋</t>
-  </si>
-  <si>
-    <t>이콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>Scania 28</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>4위</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>28명</t>
-  </si>
-  <si>
-    <t>1경 9137조 3448억 6787만</t>
-  </si>
-  <si>
-    <t>가입문의 - 요쯔</t>
-  </si>
-  <si>
-    <t>요쯔</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>냐락불곰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%B6%88%EA%B3%B0</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>1경 2229조 7494억 2484만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>냐락오리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%98%A4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>2154조 8718억 7131만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>썬콜법사님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%AC%EB%8B%98</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>2080조 4719억 3396만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>냐락겅듀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EA%B2%85%EB%93%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>1972조 9857억 9778만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>벽서</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%BD%EC%84%9C</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>1344조 2346억 7402만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>바럄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EB%9F%84</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>875조 7755억 8766만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%A7%90</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>823조 1358억 7794만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>이대팔가르마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8C%80%ED%8C%94%EA%B0%80%EB%A5%B4%EB%A7%88</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>739조 9535억 2604만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>닭도리도리탕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AD%EB%8F%84%EB%A6%AC%EB%8F%84%EB%A6%AC%ED%83%95</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>737조 8866억 8253만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>눈꽃체리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%88%EA%BD%83%EC%B2%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>456조 5442억 584만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>망치두고튀어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%91%90%EA%B3%A0%ED%8A%80%EC%96%B4</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>391조 5083억 9813만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>냐락크리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%ED%81%AC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>291조 427억 7174만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>떠네쨩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%EB%84%A4%EC%A8%A9</t>
-  </si>
-  <si>
-    <t>287조 4087억 5796만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>왕푸맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%ED%91%B8%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>255조 2513억 2505만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>냐락셋째</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%85%8B%EC%A7%B8</t>
-  </si>
-  <si>
-    <t>199조 1954억 8586만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>냐락린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>170조 6456억 3813만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>냐락쿠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%BF%A0</t>
-  </si>
-  <si>
-    <t>167조 4498억 971만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>쀼움</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%80%BC%EC%9B%80</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>152조 1480억 9079만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>샤미다미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EB%AF%B8%EB%8B%A4%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>116조 7764억 2703만</t>
-  </si>
-  <si>
-    <t>냐락뀨리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%80%A8%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>104조 9072억 7456만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>Cerberus</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Cerberus</t>
-  </si>
-  <si>
-    <t>103조 1944억 1367만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>삼양일짱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EC%96%91%EC%9D%BC%EC%A7%B1</t>
-  </si>
-  <si>
-    <t>101조 3977억 9940만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>안지연</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%A7%80%EC%97%B0</t>
-  </si>
-  <si>
-    <t>100조 4208억 8455만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>와칸다검식이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%80%EC%B9%B8%EB%8B%A4%EA%B2%80%EC%8B%9D%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>80조 2495억 315만</t>
-  </si>
-  <si>
-    <t>이강민둥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B0%95%EB%AF%BC%EB%91%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>67조 223억 9864만</t>
-  </si>
-  <si>
-    <t>히들</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EB%93%A4</t>
-  </si>
-  <si>
-    <t>65조 1068억 8052만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>국레쏘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EB%A0%88%EC%8F%98</t>
-  </si>
-  <si>
-    <t>46조 737억 621만</t>
-  </si>
-  <si>
     <t>세정린</t>
   </si>
   <si>
@@ -620,7 +626,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B1%84%ED%9D%AC</t>
   </si>
   <si>
-    <t>35조 2281억 5841만</t>
+    <t>36조 4220억 9855만</t>
   </si>
   <si>
     <t>30</t>
@@ -632,7 +638,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B0%EB%8C%80%EA%B3%A4%EC%A4%84%EB%B0%95%EC%9D%B4</t>
   </si>
   <si>
-    <t>25조 5321억 5285만</t>
+    <t>26조 8389억 5086만</t>
   </si>
   <si>
     <t>스타냥이</t>
@@ -650,7 +656,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
   </si>
   <si>
-    <t>2811조 7824억 2640만</t>
+    <t>3086조 8008억 1349만</t>
   </si>
   <si>
     <t>진자이</t>
@@ -659,7 +665,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>1946조 6213억 5027만</t>
+    <t>1987조 1525억 3591만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -686,7 +692,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
   </si>
   <si>
-    <t>863조 4880억 8534만</t>
+    <t>877조 7132억 9545만</t>
   </si>
   <si>
     <t>스타뎀</t>
@@ -707,6 +713,15 @@
     <t>305조 8357억 2579만</t>
   </si>
   <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>136조 538억 20만</t>
+  </si>
+  <si>
     <t>프리프리</t>
   </si>
   <si>
@@ -716,6 +731,15 @@
     <t>133조 9835억 1204만</t>
   </si>
   <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>130조 1373억 6155만</t>
+  </si>
+  <si>
     <t>단풍노비</t>
   </si>
   <si>
@@ -725,22 +749,13 @@
     <t>129조 1928억 3956만</t>
   </si>
   <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>128조 2885억 4747만</t>
-  </si>
-  <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>124조 1249억 6059만</t>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>88조 2451억 2350만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -749,7 +764,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
   </si>
   <si>
-    <t>76조 9998억 392만</t>
+    <t>77조 146억 9179만</t>
   </si>
   <si>
     <t>잼포즈</t>
@@ -761,22 +776,13 @@
     <t>70조 6447억 9453만</t>
   </si>
   <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>69조 2571억 2455만</t>
-  </si>
-  <si>
     <t>하후돈</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>65조 7023억 3999만</t>
+    <t>70조 3961억 1459만</t>
   </si>
   <si>
     <t>POSCO</t>
@@ -785,7 +791,7 @@
     <t>https://mgf.gg/contents/character.php?n=POSCO</t>
   </si>
   <si>
-    <t>43조 5115억 6200만</t>
+    <t>57조 4937억 6303만</t>
   </si>
   <si>
     <t>소소채2</t>
@@ -794,315 +800,312 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
   </si>
   <si>
+    <t>40조 2500억 6433만</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>36조 4911억 1366만</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>35조 8661억 468만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>34조 7934억 9340만</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>33조 2627억 996만</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>29조 6116억 7131만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>26조 1612억 9501만</t>
+  </si>
+  <si>
+    <t>포뇨야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
+  </si>
+  <si>
+    <t>25조 4912억 9969만</t>
+  </si>
+  <si>
+    <t>울힝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
+  </si>
+  <si>
+    <t>24조 1913억 1904만</t>
+  </si>
+  <si>
+    <t>악의꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
+  </si>
+  <si>
+    <t>23조 3285억 9707만</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>22조 2478억 3221만</t>
+  </si>
+  <si>
+    <t>몽호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
+  </si>
+  <si>
+    <t>18조 665억 8429만</t>
+  </si>
+  <si>
+    <t>junoflo</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=junoflo</t>
+  </si>
+  <si>
+    <t>9조 8206억 4671만</t>
+  </si>
+  <si>
+    <t>26순혁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EC%88%9C%ED%98%81</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>1경 6443조 1834억 7428만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
+  </si>
+  <si>
+    <t>2516조 4761억 566만</t>
+  </si>
+  <si>
+    <t>26상탗</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EC%83%81%ED%83%97</t>
+  </si>
+  <si>
+    <t>1302조 2410억 2843만</t>
+  </si>
+  <si>
+    <t>뇌쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
+  </si>
+  <si>
+    <t>462조 3946억 8834만</t>
+  </si>
+  <si>
+    <t>찐빵은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EB%B9%B5%EC%9D%80</t>
+  </si>
+  <si>
+    <t>458조 182억 6021만</t>
+  </si>
+  <si>
+    <t>26길초</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
+  </si>
+  <si>
+    <t>373조 4972억 3847만</t>
+  </si>
+  <si>
+    <t>26들박</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%93%A4%EB%B0%95</t>
+  </si>
+  <si>
+    <t>310조 7616억 9372만</t>
+  </si>
+  <si>
+    <t>서예슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>264조 8423억 9852만</t>
+  </si>
+  <si>
+    <t>26빵은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%B9%B5%EC%9D%80</t>
+  </si>
+  <si>
+    <t>222조 1071억 7012만</t>
+  </si>
+  <si>
+    <t>임승민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>128조 5297억 4251만</t>
+  </si>
+  <si>
+    <t>26밍밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%8D%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>119조 856억 3291만</t>
+  </si>
+  <si>
+    <t>26횟집</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%ED%9A%9F%EC%A7%91</t>
+  </si>
+  <si>
+    <t>97조 8592억 9472만</t>
+  </si>
+  <si>
+    <t>뻔수니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
+  </si>
+  <si>
+    <t>61조 4934억 8292만</t>
+  </si>
+  <si>
+    <t>얼음깨먹기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EA%B9%A8%EB%A8%B9%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>54조 757억 7660만</t>
+  </si>
+  <si>
+    <t>26배털</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
+  </si>
+  <si>
+    <t>36조 1836억 7704만</t>
+  </si>
+  <si>
+    <t>26수빈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EC%88%98%EB%B9%88</t>
+  </si>
+  <si>
+    <t>28조 3019억 2162만</t>
+  </si>
+  <si>
+    <t>류테</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
+  </si>
+  <si>
+    <t>20조 4843억 3219만</t>
+  </si>
+  <si>
+    <t>26퐝바</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
+  </si>
+  <si>
+    <t>19조 7244억 2353만</t>
+  </si>
+  <si>
+    <t>아모르파티퀘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
+  </si>
+  <si>
+    <t>17조 8709억 3446만</t>
+  </si>
+  <si>
+    <t>뻐늬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
+  </si>
+  <si>
+    <t>16조 3733억 5727만</t>
+  </si>
+  <si>
+    <t>26조선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EC%A1%B0%EC%84%A0</t>
+  </si>
+  <si>
+    <t>15조 1898억 2101만</t>
+  </si>
+  <si>
+    <t>브깃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
+  </si>
+  <si>
     <t>101</t>
   </si>
   <si>
-    <t>35조 9805억 8583만</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>35조 532억 9817만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>34조 7934억 9340만</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>33조 856억 7988만</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>30조 6593억 8822만</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>29조 1275억 1565만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>26조 735억 6034만</t>
-  </si>
-  <si>
-    <t>포뇨야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
-  </si>
-  <si>
-    <t>25조 4912억 9969만</t>
-  </si>
-  <si>
-    <t>울힝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
-  </si>
-  <si>
-    <t>24조 1913억 1904만</t>
-  </si>
-  <si>
-    <t>악의꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
-  </si>
-  <si>
-    <t>22조 1676억 7265만</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>22조 162억 9023만</t>
-  </si>
-  <si>
-    <t>몽호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
-  </si>
-  <si>
-    <t>18조 263억 6435만</t>
-  </si>
-  <si>
-    <t>junoflo</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=junoflo</t>
-  </si>
-  <si>
-    <t>9조 4979억 5390만</t>
-  </si>
-  <si>
-    <t>26순혁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EC%88%9C%ED%98%81</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>1경 6443조 1834억 7428만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>2502조 9826억 7967만</t>
-  </si>
-  <si>
-    <t>26상탗</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EC%83%81%ED%83%97</t>
-  </si>
-  <si>
-    <t>1301조 7924억 7329만</t>
-  </si>
-  <si>
-    <t>뇌쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
-  </si>
-  <si>
-    <t>462조 3946억 8834만</t>
-  </si>
-  <si>
-    <t>찐빵은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EB%B9%B5%EC%9D%80</t>
-  </si>
-  <si>
-    <t>376조 9686억 760만</t>
-  </si>
-  <si>
-    <t>26길초</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
-  </si>
-  <si>
-    <t>372조 867억 9160만</t>
-  </si>
-  <si>
-    <t>26들박</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%93%A4%EB%B0%95</t>
-  </si>
-  <si>
-    <t>310조 6004억 7184만</t>
-  </si>
-  <si>
-    <t>서예슬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
-  </si>
-  <si>
-    <t>255조 8017억 1535만</t>
-  </si>
-  <si>
-    <t>26빵은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%B9%B5%EC%9D%80</t>
-  </si>
-  <si>
-    <t>222조 1071억 7012만</t>
-  </si>
-  <si>
-    <t>임승민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>124조 712억 140만</t>
-  </si>
-  <si>
-    <t>26밍밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%8D%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>119조 856억 3291만</t>
-  </si>
-  <si>
-    <t>26횟집</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%ED%9A%9F%EC%A7%91</t>
-  </si>
-  <si>
-    <t>96조 9899억 6229만</t>
-  </si>
-  <si>
-    <t>뻔수니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
-  </si>
-  <si>
-    <t>56조 557억 2565만</t>
-  </si>
-  <si>
-    <t>얼음깨먹기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EA%B9%A8%EB%A8%B9%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>50조 3100억 9884만</t>
-  </si>
-  <si>
-    <t>26배털</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
-  </si>
-  <si>
-    <t>31조 8267억 9814만</t>
-  </si>
-  <si>
-    <t>26수빈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EC%88%98%EB%B9%88</t>
-  </si>
-  <si>
-    <t>25조 78억 6207만</t>
-  </si>
-  <si>
-    <t>류테</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
-  </si>
-  <si>
-    <t>20조 4843억 3219만</t>
-  </si>
-  <si>
-    <t>26퐝바</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
-  </si>
-  <si>
-    <t>17조 9480억 6864만</t>
-  </si>
-  <si>
-    <t>아모르파티퀘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
-  </si>
-  <si>
-    <t>17조 1585억 8689만</t>
-  </si>
-  <si>
-    <t>뻐늬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
-  </si>
-  <si>
-    <t>16조 1989억 14만</t>
-  </si>
-  <si>
-    <t>26조선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EC%A1%B0%EC%84%A0</t>
-  </si>
-  <si>
-    <t>15조 1898억 2101만</t>
-  </si>
-  <si>
-    <t>브깃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
-  </si>
-  <si>
     <t>12조 6004억 5926만</t>
   </si>
   <si>
@@ -1121,7 +1124,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
   </si>
   <si>
-    <t>8조 8839억 1009만</t>
+    <t>9조 5687억 8045만</t>
   </si>
   <si>
     <t>뿜삐</t>
@@ -1133,7 +1136,7 @@
     <t>100</t>
   </si>
   <si>
-    <t>8조 3343억 8600만</t>
+    <t>8조 9447억 626만</t>
   </si>
   <si>
     <t>예라미</t>
@@ -1142,7 +1145,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
   </si>
   <si>
-    <t>6조 5507억 9718만</t>
+    <t>6조 5810억 9603만</t>
   </si>
   <si>
     <t>귬스파파</t>
@@ -1160,13 +1163,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%98%81%ED%9D%AC%EB%A9%88%EB%AD%84%EB%AF%B8</t>
   </si>
   <si>
-    <t>5조 2058억 6573만</t>
+    <t>5조 2715억 6966만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EA%B8%B0%EC%9A%94%EB%B0%8B</t>
   </si>
   <si>
-    <t>1경 3416조 6921억 5835만</t>
+    <t>1경 4372조 896억 1505만</t>
   </si>
   <si>
     <t>일월마녀</t>
@@ -1187,7 +1190,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%ED%92%8D</t>
   </si>
   <si>
-    <t>1154조 7823억 2893만</t>
+    <t>1188조 9600억 6159만</t>
   </si>
   <si>
     <t>로드숍</t>
@@ -1205,7 +1208,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EC%A7%9C</t>
   </si>
   <si>
-    <t>624조 598억 3395만</t>
+    <t>673조 3594억 4963만</t>
   </si>
   <si>
     <t>송곧</t>
@@ -1214,7 +1217,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EA%B3%A7</t>
   </si>
   <si>
-    <t>536조 1566억 7259만</t>
+    <t>538조 9470억 223만</t>
   </si>
   <si>
     <t>똥으리</t>
@@ -1232,7 +1235,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9D%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>171조 9276억 4935만</t>
+    <t>175조 3207억 9290만</t>
   </si>
   <si>
     <t>피몽</t>
@@ -1241,7 +1244,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EB%AA%BD</t>
   </si>
   <si>
-    <t>131조 6403억 8429만</t>
+    <t>154조 4414억 5818만</t>
   </si>
   <si>
     <t>진짜지존법사</t>
@@ -1250,7 +1253,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%A7%9C%EC%A7%80%EC%A1%B4%EB%B2%95%EC%82%AC</t>
   </si>
   <si>
-    <t>109조 2489억 3589만</t>
+    <t>116조 5809억 6591만</t>
   </si>
   <si>
     <t>원순철</t>
@@ -1268,7 +1271,7 @@
     <t>https://mgf.gg/contents/character.php?n=ADELL</t>
   </si>
   <si>
-    <t>37조 1257억 1386만</t>
+    <t>38조 45억 4257만</t>
   </si>
   <si>
     <t>쿠소가키키</t>
@@ -1286,7 +1289,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BC%B1</t>
   </si>
   <si>
-    <t>13조 7240억 3347만</t>
+    <t>14조 2076억 6876만</t>
   </si>
   <si>
     <t>왓쳐</t>
@@ -1295,7 +1298,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%93%EC%B3%90</t>
   </si>
   <si>
-    <t>12조 4928억 180만</t>
+    <t>12조 9981억 2705만</t>
   </si>
   <si>
     <t>유디티기찬</t>
@@ -1304,7 +1307,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%94%94%ED%8B%B0%EA%B8%B0%EC%B0%AC</t>
   </si>
   <si>
-    <t>11조 3222억 4934만</t>
+    <t>11조 3598억 703만</t>
   </si>
   <si>
     <t>박미쯔</t>
@@ -1325,6 +1328,15 @@
     <t>10조 5748억 5807만</t>
   </si>
   <si>
+    <t>키우는건질색</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9A%B0%EB%8A%94%EA%B1%B4%EC%A7%88%EC%83%89</t>
+  </si>
+  <si>
+    <t>8조 4789억 5075만</t>
+  </si>
+  <si>
     <t>강띵띵</t>
   </si>
   <si>
@@ -1343,15 +1355,6 @@
     <t>6조 6792억 8468만</t>
   </si>
   <si>
-    <t>키우는건질색</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9A%B0%EB%8A%94%EA%B1%B4%EC%A7%88%EC%83%89</t>
-  </si>
-  <si>
-    <t>6조 4672억 7973만</t>
-  </si>
-  <si>
     <t>후아멀로하냐</t>
   </si>
   <si>
@@ -1361,7 +1364,7 @@
     <t>99</t>
   </si>
   <si>
-    <t>5조 8473억 6277만</t>
+    <t>6조 1297억 4182만</t>
   </si>
   <si>
     <t>햄쓱이</t>
@@ -1382,7 +1385,7 @@
     <t>98</t>
   </si>
   <si>
-    <t>4조 8708억 1278만</t>
+    <t>5조 2081억 4052만</t>
   </si>
   <si>
     <t>술취한호랑이</t>
@@ -1391,7 +1394,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EC%B7%A8%ED%95%9C%ED%98%B8%EB%9E%91%EC%9D%B4</t>
   </si>
   <si>
-    <t>4조 4630억 8275만</t>
+    <t>4조 8734억 8870만</t>
   </si>
   <si>
     <t>한Poll</t>
@@ -1400,7 +1403,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9CPoll</t>
   </si>
   <si>
-    <t>3조 9956억 1684만</t>
+    <t>4조 299억 264만</t>
   </si>
   <si>
     <t>수년</t>
@@ -1409,7 +1412,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%85%84</t>
   </si>
   <si>
-    <t>3조 8612억 4341만</t>
+    <t>4조 64억 658만</t>
   </si>
   <si>
     <t>김치왕뚜껑</t>
@@ -1418,7 +1421,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%99%95%EB%9A%9C%EA%BB%91</t>
   </si>
   <si>
-    <t>3조 4955억 2414만</t>
+    <t>3조 8849억 2658만</t>
   </si>
   <si>
     <t>쿠쏘야로로</t>
@@ -1427,7 +1430,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%8F%98%EC%95%BC%EB%A1%9C%EB%A1%9C</t>
   </si>
   <si>
-    <t>2조 3439억 9014만</t>
+    <t>2조 4554억 6648만</t>
   </si>
   <si>
     <t>치즈왕뚜껑</t>
@@ -1436,7 +1439,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%A6%88%EC%99%95%EB%9A%9C%EA%BB%91</t>
   </si>
   <si>
-    <t>2조 1538억 2144만</t>
+    <t>2조 1657억 1197만</t>
   </si>
   <si>
     <t>신궁쨩</t>
@@ -1454,7 +1457,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
   </si>
   <si>
-    <t>7064조 1272억 3711만</t>
+    <t>7161조 3638억 2994만</t>
   </si>
   <si>
     <t>실민</t>
@@ -1472,7 +1475,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
   </si>
   <si>
-    <t>720조 4647억 4246만</t>
+    <t>732조 9186억 8857만</t>
   </si>
   <si>
     <t>민실</t>
@@ -1481,7 +1484,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%8B%A4</t>
   </si>
   <si>
-    <t>568조 5879억 7585만</t>
+    <t>623조 1792억 4623만</t>
   </si>
   <si>
     <t>앨삐</t>
@@ -1490,7 +1493,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EC%82%90</t>
   </si>
   <si>
-    <t>265조 7402억 6624만</t>
+    <t>298조 4629억 4887만</t>
   </si>
   <si>
     <t>문디르</t>
@@ -1499,7 +1502,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
   </si>
   <si>
-    <t>188조 2968억 5490만</t>
+    <t>206조 8757억 5344만</t>
   </si>
   <si>
     <t>항상밝은하루</t>
@@ -1544,7 +1547,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%8F%AC%EC%9D%98%EC%98%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>59조 7852억 2884만</t>
+    <t>60조 752억 9194만</t>
+  </si>
+  <si>
+    <t>꽃나래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
+  </si>
+  <si>
+    <t>44조 2729억 5365만</t>
   </si>
   <si>
     <t>은달총</t>
@@ -1553,16 +1565,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%AC%EC%B4%9D</t>
   </si>
   <si>
-    <t>37조 9875억 239만</t>
-  </si>
-  <si>
-    <t>꽃나래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
-  </si>
-  <si>
-    <t>37조 8956억 2896만</t>
+    <t>38조 9416억 5281만</t>
   </si>
   <si>
     <t>김대협</t>
@@ -1571,7 +1574,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8C%80%ED%98%91</t>
   </si>
   <si>
-    <t>22조 2718억 3445만</t>
+    <t>23조 6540억 5623만</t>
+  </si>
+  <si>
+    <t>뽀라비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
+  </si>
+  <si>
+    <t>22조 1068억 9929만</t>
   </si>
   <si>
     <t>땩콩</t>
@@ -1580,7 +1592,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
   </si>
   <si>
-    <t>21조 7998억 5419만</t>
+    <t>21조 9833억 8948만</t>
   </si>
   <si>
     <t>에망</t>
@@ -1589,7 +1601,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
   </si>
   <si>
-    <t>11조 7922억 1619만</t>
+    <t>12조 5545억 1110만</t>
   </si>
   <si>
     <t>낭만만듀</t>
@@ -1607,7 +1619,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EB%85%98</t>
   </si>
   <si>
-    <t>8조 5071억 3693만</t>
+    <t>8조 8066억 7996만</t>
   </si>
   <si>
     <t>다송이</t>
@@ -1616,7 +1628,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
   </si>
   <si>
-    <t>7조 6214억 2565만</t>
+    <t>7조 8427억 4237만</t>
   </si>
   <si>
     <t>빠나딘</t>
@@ -1634,7 +1646,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
   </si>
   <si>
-    <t>5조 6976억 9508만</t>
+    <t>6조 7354억 3533만</t>
   </si>
   <si>
     <t>양카오너</t>
@@ -1643,28 +1655,37 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%B9%B4%EC%98%A4%EB%84%88</t>
   </si>
   <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>3조 3513억 5154만</t>
+  </si>
+  <si>
+    <t>강한고등어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
+  </si>
+  <si>
+    <t>2조 4727억 9722만</t>
+  </si>
+  <si>
+    <t>돌쇠영만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
+  </si>
+  <si>
     <t>96</t>
   </si>
   <si>
-    <t>2조 4997억 7676만</t>
-  </si>
-  <si>
-    <t>강한고등어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
-  </si>
-  <si>
-    <t>2조 4534억 4841만</t>
-  </si>
-  <si>
-    <t>돌쇠영만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
-  </si>
-  <si>
-    <t>1조 77억 4734만</t>
+    <t>1조 206억 7862만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
+  </si>
+  <si>
+    <t>6421억 9963만</t>
   </si>
   <si>
     <t>용광사</t>
@@ -1676,13 +1697,7 @@
     <t>95</t>
   </si>
   <si>
-    <t>5941억 677만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
-  </si>
-  <si>
-    <t>5446억 9840만</t>
+    <t>6011억 6649만</t>
   </si>
   <si>
     <t>비어치킨</t>
@@ -2193,45 +2208,45 @@
         <v>31</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>24</v>
@@ -2239,22 +2254,22 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>18</v>
@@ -2266,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>24</v>
@@ -2280,40 +2295,40 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>24</v>
@@ -2352,28 +2367,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2384,28 +2399,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2416,28 +2431,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2448,28 +2463,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2480,28 +2495,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2512,28 +2527,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2544,28 +2559,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2576,7 +2591,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>23</v>
@@ -2585,19 +2600,19 @@
         <v>23</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2608,28 +2623,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2640,28 +2655,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2672,28 +2687,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2704,28 +2719,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2736,28 +2751,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2768,28 +2783,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2800,28 +2815,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2832,28 +2847,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="I16" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2864,28 +2879,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2896,28 +2911,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2928,28 +2943,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2960,28 +2975,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>157</v>
+        <v>124</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -2995,25 +3010,25 @@
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3024,28 +3039,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3056,28 +3071,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3088,28 +3103,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3120,28 +3135,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3152,28 +3167,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3184,28 +3199,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3216,28 +3231,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3248,28 +3263,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3280,28 +3295,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3312,28 +3327,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3397,28 +3412,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3429,31 +3444,31 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3461,31 +3476,31 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3493,31 +3508,31 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3525,31 +3540,31 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3557,31 +3572,31 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3589,31 +3604,31 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3621,31 +3636,31 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3653,31 +3668,31 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3685,31 +3700,31 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3717,31 +3732,31 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3749,31 +3764,31 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3781,31 +3796,31 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3813,31 +3828,31 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3845,31 +3860,31 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3877,31 +3892,31 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -3909,31 +3924,31 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -3941,31 +3956,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -3973,31 +3988,31 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>255</v>
+        <v>164</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -4005,31 +4020,31 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4040,28 +4055,28 @@
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4069,31 +4084,31 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4101,31 +4116,31 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4133,31 +4148,31 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4165,7 +4180,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>31</v>
@@ -4174,22 +4189,22 @@
         <v>31</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4197,31 +4212,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4229,31 +4244,31 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4261,31 +4276,31 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -4293,31 +4308,31 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -4325,31 +4340,31 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -4357,31 +4372,31 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -4442,28 +4457,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4471,31 +4486,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4503,28 +4518,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>297</v>
+        <v>77</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>298</v>
@@ -4535,10 +4550,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>299</v>
@@ -4550,13 +4565,13 @@
         <v>300</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>301</v>
@@ -4567,10 +4582,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>302</v>
@@ -4582,13 +4597,13 @@
         <v>303</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>304</v>
@@ -4599,10 +4614,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>305</v>
@@ -4614,13 +4629,13 @@
         <v>306</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>307</v>
@@ -4631,10 +4646,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>308</v>
@@ -4646,13 +4661,13 @@
         <v>309</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>310</v>
@@ -4663,10 +4678,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>311</v>
@@ -4678,13 +4693,13 @@
         <v>312</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>313</v>
@@ -4695,10 +4710,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>314</v>
@@ -4710,13 +4725,13 @@
         <v>315</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>316</v>
@@ -4727,10 +4742,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>317</v>
@@ -4742,13 +4757,13 @@
         <v>318</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>319</v>
@@ -4759,10 +4774,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>320</v>
@@ -4774,13 +4789,13 @@
         <v>321</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>322</v>
@@ -4791,10 +4806,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>323</v>
@@ -4806,13 +4821,13 @@
         <v>324</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>325</v>
@@ -4823,10 +4838,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>326</v>
@@ -4838,13 +4853,13 @@
         <v>327</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>328</v>
@@ -4855,10 +4870,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>329</v>
@@ -4870,13 +4885,13 @@
         <v>330</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>331</v>
@@ -4887,10 +4902,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>332</v>
@@ -4902,13 +4917,13 @@
         <v>333</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>334</v>
@@ -4919,10 +4934,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>335</v>
@@ -4934,13 +4949,13 @@
         <v>336</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>337</v>
@@ -4951,10 +4966,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>338</v>
@@ -4966,13 +4981,13 @@
         <v>339</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>340</v>
@@ -4983,10 +4998,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>341</v>
@@ -4998,13 +5013,13 @@
         <v>342</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>343</v>
@@ -5015,10 +5030,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>344</v>
@@ -5030,13 +5045,13 @@
         <v>345</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>346</v>
@@ -5047,10 +5062,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>347</v>
@@ -5062,13 +5077,13 @@
         <v>348</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>349</v>
@@ -5079,7 +5094,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>17</v>
@@ -5094,13 +5109,13 @@
         <v>351</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>352</v>
@@ -5111,10 +5126,10 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>353</v>
@@ -5126,13 +5141,13 @@
         <v>354</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>355</v>
@@ -5143,10 +5158,10 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>356</v>
@@ -5158,16 +5173,16 @@
         <v>357</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5175,31 +5190,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5207,31 +5222,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5239,31 +5254,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5271,31 +5286,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5303,31 +5318,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5335,31 +5350,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5412,7 +5427,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5421,28 +5436,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5450,31 +5465,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5482,31 +5497,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5514,31 +5529,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5546,31 +5561,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5578,31 +5593,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5610,31 +5625,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5642,31 +5657,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5674,31 +5689,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5706,31 +5721,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5738,31 +5753,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5770,31 +5785,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5802,31 +5817,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5834,31 +5849,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5866,31 +5881,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5898,31 +5913,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5930,31 +5945,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5962,31 +5977,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5994,31 +6009,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6026,31 +6041,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>255</v>
+        <v>368</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6058,31 +6073,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6090,31 +6105,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6122,31 +6137,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6154,31 +6169,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6186,31 +6201,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6218,31 +6233,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6250,31 +6265,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6282,31 +6297,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6314,31 +6329,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6346,31 +6361,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6378,31 +6393,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6448,7 +6463,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -6466,28 +6481,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6495,31 +6510,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6527,31 +6542,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>297</v>
+        <v>77</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6559,31 +6574,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6591,31 +6606,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6623,31 +6638,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6655,31 +6670,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6687,31 +6702,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6719,31 +6734,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6751,31 +6766,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6783,31 +6798,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6815,31 +6830,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6847,31 +6862,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6879,31 +6894,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6911,31 +6926,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6943,31 +6958,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6975,31 +6990,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7007,31 +7022,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>367</v>
+        <v>164</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7039,31 +7054,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7071,31 +7086,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7103,31 +7118,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7135,31 +7150,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7167,31 +7182,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>443</v>
+        <v>368</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7199,28 +7214,28 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>538</v>
+        <v>368</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>539</v>
@@ -7231,10 +7246,10 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>540</v>
@@ -7246,16 +7261,16 @@
         <v>541</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>157</v>
+        <v>99</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>443</v>
+        <v>542</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7263,31 +7278,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>538</v>
+        <v>444</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7295,31 +7310,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7327,31 +7342,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7359,38 +7374,70 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -7420,6 +7467,7 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/셀린느/셀린느_mgf_matched_5_guilds.xlsx
+++ b/reports/셀린느/셀린느_mgf_matched_5_guilds.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">LUXURY!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">LUXURY!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">냐락!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">셀린느!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">이콩!$A$1:$J$30</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="564">
   <si>
     <t>guild_name</t>
   </si>
@@ -248,12 +248,30 @@
     <t>113</t>
   </si>
   <si>
-    <t>1경 2229조 7494억 2484만</t>
+    <t>1경 2948조 1752억 3433만</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>냐락겅듀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EA%B2%85%EB%93%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>2296조 6952억 7221만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>냐락오리</t>
   </si>
   <si>
@@ -263,10 +281,10 @@
     <t>110</t>
   </si>
   <si>
-    <t>2162조 4673억 382만</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>2211조 5187억 5797만</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>썬콜법사님</t>
@@ -278,78 +296,60 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>2149조 1176억 4861만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>냐락겅듀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EA%B2%85%EB%93%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
+    <t>2183조 6870억 5466만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>벽서</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%BD%EC%84%9C</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>1395조 8364억 2120만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%A7%90</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>882조 2647억 5698만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>냐락바람</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%B0%94%EB%9E%8C</t>
+  </si>
+  <si>
+    <t>히어로</t>
   </si>
   <si>
     <t>108</t>
   </si>
   <si>
-    <t>1982조 8748억 2848만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>벽서</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%BD%EC%84%9C</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>1389조 2663억 3276만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>냐락바람</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%B0%94%EB%9E%8C</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
     <t>875조 7755억 8766만</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%A7%90</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>827조 5226억 4948만</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
@@ -362,7 +362,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>742조 6263억 3641만</t>
+    <t>777조 6064억 4990만</t>
   </si>
   <si>
     <t>9</t>
@@ -374,49 +374,49 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8C%80%ED%8C%94%EA%B0%80%EB%A5%B4%EB%A7%88</t>
   </si>
   <si>
+    <t>744조 9863억 2699만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>눈꽃체리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%88%EA%BD%83%EC%B2%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>500조 7087억 496만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>망치두고튀어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%91%90%EA%B3%A0%ED%8A%80%EC%96%B4</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>417조 4654억 638만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>냐락크리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%ED%81%AC%EB%A6%AC</t>
+  </si>
+  <si>
     <t>106</t>
   </si>
   <si>
-    <t>739조 9535억 2604만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>눈꽃체리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%88%EA%BD%83%EC%B2%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>464조 9749억 4990만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>망치두고튀어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%91%90%EA%B3%A0%ED%8A%80%EC%96%B4</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>391조 5083억 9813만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>냐락크리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%ED%81%AC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>291조 427억 7174만</t>
+    <t>310조 5226억 5741만</t>
   </si>
   <si>
     <t>13</t>
@@ -428,7 +428,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%EB%84%A4%EC%A8%A9</t>
   </si>
   <si>
-    <t>287조 4087억 5796만</t>
+    <t>288조 889억 3277만</t>
   </si>
   <si>
     <t>14</t>
@@ -443,7 +443,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>274조 9324억 390만</t>
+    <t>276조 590억 1583만</t>
   </si>
   <si>
     <t>15</t>
@@ -455,7 +455,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%85%8B%EC%A7%B8</t>
   </si>
   <si>
-    <t>200조 1259억 9854만</t>
+    <t>206조 8490억 5257만</t>
   </si>
   <si>
     <t>16</t>
@@ -479,7 +479,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%BF%A0</t>
   </si>
   <si>
-    <t>168조 2748억 1327만</t>
+    <t>168조 8233억 7615만</t>
   </si>
   <si>
     <t>18</t>
@@ -494,7 +494,7 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>152조 1480억 9079만</t>
+    <t>157조 1751억 7341만</t>
   </si>
   <si>
     <t>19</t>
@@ -530,6 +530,18 @@
     <t>21</t>
   </si>
   <si>
+    <t>안지연</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%A7%80%EC%97%B0</t>
+  </si>
+  <si>
+    <t>115조 1259억 5158만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>냐락뀨리</t>
   </si>
   <si>
@@ -539,18 +551,6 @@
     <t>104조 9239억 1201만</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>안지연</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%A7%80%EC%97%B0</t>
-  </si>
-  <si>
-    <t>103조 5157억 8876만</t>
-  </si>
-  <si>
     <t>23</t>
   </si>
   <si>
@@ -560,7 +560,7 @@
     <t>https://mgf.gg/contents/character.php?n=Cerberus</t>
   </si>
   <si>
-    <t>103조 4463억 3620만</t>
+    <t>103조 5381억 493만</t>
   </si>
   <si>
     <t>24</t>
@@ -572,28 +572,28 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%80%EC%B9%B8%EB%8B%A4%EA%B2%80%EC%8B%9D%EC%9D%B4</t>
   </si>
   <si>
+    <t>101조 4237억 4479만</t>
+  </si>
+  <si>
+    <t>이강민둥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B0%95%EB%AF%BC%EB%91%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>67조 223억 9864만</t>
+  </si>
+  <si>
+    <t>히들</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EB%93%A4</t>
+  </si>
+  <si>
     <t>103</t>
   </si>
   <si>
-    <t>80조 2495억 315만</t>
-  </si>
-  <si>
-    <t>이강민둥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B0%95%EB%AF%BC%EB%91%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>67조 223억 9864만</t>
-  </si>
-  <si>
-    <t>히들</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EB%93%A4</t>
-  </si>
-  <si>
-    <t>65조 1068억 8052만</t>
+    <t>66조 5056억 7788만</t>
   </si>
   <si>
     <t>국레쏘</t>
@@ -602,12 +602,24 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EB%A0%88%EC%8F%98</t>
   </si>
   <si>
-    <t>50조 896억 2626만</t>
+    <t>59조 2958억 2118만</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
+    <t>김채희</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B1%84%ED%9D%AC</t>
+  </si>
+  <si>
+    <t>38조 900억 7159만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
     <t>세정린</t>
   </si>
   <si>
@@ -617,18 +629,6 @@
     <t>37조 5529억 1971만</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>김채희</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B1%84%ED%9D%AC</t>
-  </si>
-  <si>
-    <t>36조 4220억 9855만</t>
-  </si>
-  <si>
     <t>30</t>
   </si>
   <si>
@@ -638,7 +638,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B0%EB%8C%80%EA%B3%A4%EC%A4%84%EB%B0%95%EC%9D%B4</t>
   </si>
   <si>
-    <t>26조 8389억 5086만</t>
+    <t>33조 5705억 4164만</t>
   </si>
   <si>
     <t>스타냥이</t>
@@ -656,7 +656,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
   </si>
   <si>
-    <t>3086조 8008억 1349만</t>
+    <t>3322조 3154억 8065만</t>
   </si>
   <si>
     <t>진자이</t>
@@ -665,7 +665,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>1987조 1525억 3591만</t>
+    <t>2077조 7738억 8253만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -683,7 +683,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
   </si>
   <si>
-    <t>962조 3461억 8276만</t>
+    <t>978조 7665억 8728만</t>
   </si>
   <si>
     <t>빌런투킬</t>
@@ -692,7 +692,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
   </si>
   <si>
-    <t>877조 7132억 9545만</t>
+    <t>933조 5078억 2755만</t>
   </si>
   <si>
     <t>스타뎀</t>
@@ -701,7 +701,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
   </si>
   <si>
-    <t>314조 945억 4256만</t>
+    <t>314조 5879억 8957만</t>
   </si>
   <si>
     <t>여사</t>
@@ -713,13 +713,31 @@
     <t>305조 8357억 2579만</t>
   </si>
   <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>165조 4170억 907만</t>
+  </si>
+  <si>
     <t>약어</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
   </si>
   <si>
-    <t>136조 538억 20만</t>
+    <t>147조 7288억 7111만</t>
+  </si>
+  <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>137조 9189억 5210만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -731,31 +749,13 @@
     <t>133조 9835억 1204만</t>
   </si>
   <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>130조 1373억 6155만</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>129조 1928억 3956만</t>
-  </si>
-  <si>
     <t>꽃을든남자</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>88조 2451억 2350만</t>
+    <t>117조 2807억 9343만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -764,7 +764,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
   </si>
   <si>
-    <t>77조 146억 9179만</t>
+    <t>85조 1744억 8515만</t>
   </si>
   <si>
     <t>잼포즈</t>
@@ -773,7 +773,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>70조 6447억 9453만</t>
+    <t>71조 5763억 8505만</t>
   </si>
   <si>
     <t>하후돈</t>
@@ -791,7 +791,7 @@
     <t>https://mgf.gg/contents/character.php?n=POSCO</t>
   </si>
   <si>
-    <t>57조 4937억 6303만</t>
+    <t>59조 1651억 31만</t>
   </si>
   <si>
     <t>소소채2</t>
@@ -800,7 +800,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
   </si>
   <si>
-    <t>40조 2500억 6433만</t>
+    <t>56조 1022억 3684만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>37조 1057억 885만</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>36조 8904억 6796만</t>
   </si>
   <si>
     <t>김치싸대기</t>
@@ -809,25 +827,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
   </si>
   <si>
-    <t>36조 4911억 1366만</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>35조 8661억 468만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>34조 7934억 9340만</t>
+    <t>36조 6013억 1317만</t>
   </si>
   <si>
     <t>두근푸근연근</t>
@@ -836,7 +836,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
   </si>
   <si>
-    <t>33조 2627억 996만</t>
+    <t>33조 7492억 4506만</t>
   </si>
   <si>
     <t>대방어조아</t>
@@ -845,13 +845,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>29조 6116억 7131만</t>
+    <t>31조 4997억 1522만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>26조 1612억 9501만</t>
+    <t>28조 2054억 3268만</t>
+  </si>
+  <si>
+    <t>울힝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
+  </si>
+  <si>
+    <t>26조 3529억 5204만</t>
   </si>
   <si>
     <t>포뇨야</t>
@@ -863,13 +872,13 @@
     <t>25조 4912억 9969만</t>
   </si>
   <si>
-    <t>울힝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
-  </si>
-  <si>
-    <t>24조 1913억 1904만</t>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>23조 3910억 228만</t>
   </si>
   <si>
     <t>악의꽃</t>
@@ -881,22 +890,13 @@
     <t>23조 3285억 9707만</t>
   </si>
   <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>22조 2478억 3221만</t>
-  </si>
-  <si>
     <t>몽호</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
   </si>
   <si>
-    <t>18조 665억 8429만</t>
+    <t>21조 327억 3756만</t>
   </si>
   <si>
     <t>junoflo</t>
@@ -908,268 +908,280 @@
     <t>9조 8206억 4671만</t>
   </si>
   <si>
-    <t>26순혁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EC%88%9C%ED%98%81</t>
+    <t>가숭혁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%88%AD%ED%98%81</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 6991조 8873억 8940만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
+  </si>
+  <si>
+    <t>2516조 4761억 566만</t>
+  </si>
+  <si>
+    <t>26상탗</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EC%83%81%ED%83%97</t>
+  </si>
+  <si>
+    <t>1307조 3651억 6640만</t>
+  </si>
+  <si>
+    <t>달싹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
+  </si>
+  <si>
+    <t>608조 7932억 5418만</t>
+  </si>
+  <si>
+    <t>뇌쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
+  </si>
+  <si>
+    <t>462조 3946억 8834만</t>
+  </si>
+  <si>
+    <t>26길초</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
+  </si>
+  <si>
+    <t>423조 609억 3629만</t>
+  </si>
+  <si>
+    <t>26들박</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%93%A4%EB%B0%95</t>
+  </si>
+  <si>
+    <t>329조 7132억 4310만</t>
+  </si>
+  <si>
+    <t>서예슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>272조 1241억 8322만</t>
+  </si>
+  <si>
+    <t>옴짝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
+  </si>
+  <si>
+    <t>222조 1071억 7012만</t>
+  </si>
+  <si>
+    <t>임승민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>142조 5227억 3133만</t>
+  </si>
+  <si>
+    <t>몬함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
+  </si>
+  <si>
+    <t>124조 7535억 8679만</t>
+  </si>
+  <si>
+    <t>26밍밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%8D%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>119조 856억 3291만</t>
+  </si>
+  <si>
+    <t>뻔수니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
+  </si>
+  <si>
+    <t>70조 1185억 192만</t>
+  </si>
+  <si>
+    <t>얼음깨먹기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EA%B9%A8%EB%A8%B9%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>54조 757억 7660만</t>
+  </si>
+  <si>
+    <t>26배털</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
+  </si>
+  <si>
+    <t>37조 2242억 936만</t>
+  </si>
+  <si>
+    <t>쑤삔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
+  </si>
+  <si>
+    <t>28조 3019억 2162만</t>
+  </si>
+  <si>
+    <t>류테</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
+  </si>
+  <si>
+    <t>20조 6247억 8310만</t>
+  </si>
+  <si>
+    <t>26퐝바</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
+  </si>
+  <si>
+    <t>19조 7244억 2353만</t>
+  </si>
+  <si>
+    <t>아모르파티퀘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
+  </si>
+  <si>
+    <t>17조 8709억 3446만</t>
+  </si>
+  <si>
+    <t>뻐늬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
+  </si>
+  <si>
+    <t>16조 5068억 5050만</t>
+  </si>
+  <si>
+    <t>26조선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EC%A1%B0%EC%84%A0</t>
+  </si>
+  <si>
+    <t>15조 1898억 2101만</t>
+  </si>
+  <si>
+    <t>메키무라딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>15조 637억 960만</t>
+  </si>
+  <si>
+    <t>브깃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
+  </si>
+  <si>
+    <t>12조 6004억 5926만</t>
+  </si>
+  <si>
+    <t>최씨용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%94%A8%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>12조 1214억 5182만</t>
+  </si>
+  <si>
+    <t>크앙레몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>9조 5687억 8045만</t>
+  </si>
+  <si>
+    <t>뿜삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
+  </si>
+  <si>
+    <t>8조 9447억 626만</t>
+  </si>
+  <si>
+    <t>귬스파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%AC%EC%8A%A4%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>6조 8903억 4281만</t>
+  </si>
+  <si>
+    <t>예라미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>6조 6146억 1716만</t>
+  </si>
+  <si>
+    <t>고영희멈뭄미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%98%81%ED%9D%AC%EB%A9%88%EB%AD%84%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>5조 8558억 8323만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EA%B8%B0%EC%9A%94%EB%B0%8B</t>
   </si>
   <si>
     <t>111</t>
   </si>
   <si>
-    <t>1경 6443조 1834억 7428만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
-  </si>
-  <si>
-    <t>2516조 4761억 566만</t>
-  </si>
-  <si>
-    <t>26상탗</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EC%83%81%ED%83%97</t>
-  </si>
-  <si>
-    <t>1302조 2410억 2843만</t>
-  </si>
-  <si>
-    <t>뇌쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
-  </si>
-  <si>
-    <t>462조 3946억 8834만</t>
-  </si>
-  <si>
-    <t>찐빵은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EB%B9%B5%EC%9D%80</t>
-  </si>
-  <si>
-    <t>458조 182억 6021만</t>
-  </si>
-  <si>
-    <t>26길초</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
-  </si>
-  <si>
-    <t>373조 4972억 3847만</t>
-  </si>
-  <si>
-    <t>26들박</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%93%A4%EB%B0%95</t>
-  </si>
-  <si>
-    <t>310조 7616억 9372만</t>
-  </si>
-  <si>
-    <t>서예슬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
-  </si>
-  <si>
-    <t>264조 8423억 9852만</t>
-  </si>
-  <si>
-    <t>26빵은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%B9%B5%EC%9D%80</t>
-  </si>
-  <si>
-    <t>222조 1071억 7012만</t>
-  </si>
-  <si>
-    <t>임승민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>128조 5297억 4251만</t>
-  </si>
-  <si>
-    <t>26밍밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%8D%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>119조 856억 3291만</t>
-  </si>
-  <si>
-    <t>26횟집</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%ED%9A%9F%EC%A7%91</t>
-  </si>
-  <si>
-    <t>97조 8592억 9472만</t>
-  </si>
-  <si>
-    <t>뻔수니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
-  </si>
-  <si>
-    <t>61조 4934억 8292만</t>
-  </si>
-  <si>
-    <t>얼음깨먹기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EA%B9%A8%EB%A8%B9%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>54조 757억 7660만</t>
-  </si>
-  <si>
-    <t>26배털</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
-  </si>
-  <si>
-    <t>36조 1836억 7704만</t>
-  </si>
-  <si>
-    <t>26수빈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EC%88%98%EB%B9%88</t>
-  </si>
-  <si>
-    <t>28조 3019억 2162만</t>
-  </si>
-  <si>
-    <t>류테</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
-  </si>
-  <si>
-    <t>20조 4843억 3219만</t>
-  </si>
-  <si>
-    <t>26퐝바</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
-  </si>
-  <si>
-    <t>19조 7244억 2353만</t>
-  </si>
-  <si>
-    <t>아모르파티퀘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
-  </si>
-  <si>
-    <t>17조 8709억 3446만</t>
-  </si>
-  <si>
-    <t>뻐늬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
-  </si>
-  <si>
-    <t>16조 3733억 5727만</t>
-  </si>
-  <si>
-    <t>26조선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EC%A1%B0%EC%84%A0</t>
-  </si>
-  <si>
-    <t>15조 1898억 2101만</t>
-  </si>
-  <si>
-    <t>브깃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>12조 6004억 5926만</t>
-  </si>
-  <si>
-    <t>최씨용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%94%A8%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>12조 1214억 5182만</t>
-  </si>
-  <si>
-    <t>크앙레몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>9조 5687억 8045만</t>
-  </si>
-  <si>
-    <t>뿜삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>8조 9447억 626만</t>
-  </si>
-  <si>
-    <t>예라미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>6조 5810억 9603만</t>
-  </si>
-  <si>
-    <t>귬스파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%AC%EC%8A%A4%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>5조 5721억 1117만</t>
-  </si>
-  <si>
-    <t>고영희멈뭄미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%98%81%ED%9D%AC%EB%A9%88%EB%AD%84%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>5조 2715억 6966만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EA%B8%B0%EC%9A%94%EB%B0%8B</t>
-  </si>
-  <si>
-    <t>1경 4372조 896억 1505만</t>
+    <t>1경 5137조 5318억 6677만</t>
   </si>
   <si>
     <t>일월마녀</t>
@@ -1178,9 +1190,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%EC%9B%94%EB%A7%88%EB%85%80</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>4378조 604억 9661만</t>
   </si>
   <si>
@@ -1190,7 +1199,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%ED%92%8D</t>
   </si>
   <si>
-    <t>1188조 9600억 6159만</t>
+    <t>1477조 4447억 9081만</t>
   </si>
   <si>
     <t>로드숍</t>
@@ -1199,7 +1208,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%93%9C%EC%88%8D</t>
   </si>
   <si>
-    <t>764조 3776억 8930만</t>
+    <t>790조 4923억 9555만</t>
   </si>
   <si>
     <t>누짜</t>
@@ -1208,7 +1217,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EC%A7%9C</t>
   </si>
   <si>
-    <t>673조 3594억 4963만</t>
+    <t>691조 3520억 132만</t>
   </si>
   <si>
     <t>송곧</t>
@@ -1217,7 +1226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EA%B3%A7</t>
   </si>
   <si>
-    <t>538조 9470억 223만</t>
+    <t>581조 5500억 3401만</t>
   </si>
   <si>
     <t>똥으리</t>
@@ -1226,7 +1235,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EC%9C%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>246조 1144억 5306만</t>
+    <t>266조 8506억 6360만</t>
   </si>
   <si>
     <t>다이사</t>
@@ -1235,7 +1244,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9D%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>175조 3207억 9290만</t>
+    <t>183조 1156억 7543만</t>
   </si>
   <si>
     <t>피몽</t>
@@ -1244,7 +1253,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EB%AA%BD</t>
   </si>
   <si>
-    <t>154조 4414억 5818만</t>
+    <t>172조 2611억 5897만</t>
   </si>
   <si>
     <t>진짜지존법사</t>
@@ -1262,7 +1271,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%88%9C%EC%B2%A0</t>
   </si>
   <si>
-    <t>43조 9652억 6611만</t>
+    <t>47조 2419억 4473만</t>
   </si>
   <si>
     <t>ADELL</t>
@@ -1271,7 +1280,16 @@
     <t>https://mgf.gg/contents/character.php?n=ADELL</t>
   </si>
   <si>
-    <t>38조 45억 4257만</t>
+    <t>39조 2155억 5761만</t>
+  </si>
+  <si>
+    <t>태켱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BC%B1</t>
+  </si>
+  <si>
+    <t>19조 5492억 8560만</t>
   </si>
   <si>
     <t>쿠소가키키</t>
@@ -1280,16 +1298,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%86%8C%EA%B0%80%ED%82%A4%ED%82%A4</t>
   </si>
   <si>
-    <t>18조 706억 7816만</t>
-  </si>
-  <si>
-    <t>태켱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BC%B1</t>
-  </si>
-  <si>
-    <t>14조 2076억 6876만</t>
+    <t>19조 3549억 5667만</t>
   </si>
   <si>
     <t>왓쳐</t>
@@ -1298,7 +1307,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%93%EC%B3%90</t>
   </si>
   <si>
-    <t>12조 9981억 2705만</t>
+    <t>13조 226억 8271만</t>
   </si>
   <si>
     <t>유디티기찬</t>
@@ -1307,7 +1316,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%94%94%ED%8B%B0%EA%B8%B0%EC%B0%AC</t>
   </si>
   <si>
-    <t>11조 3598억 703만</t>
+    <t>11조 9560억 3534만</t>
   </si>
   <si>
     <t>박미쯔</t>
@@ -1328,6 +1337,15 @@
     <t>10조 5748억 5807만</t>
   </si>
   <si>
+    <t>강띵띵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%9D%B5%EB%9D%B5</t>
+  </si>
+  <si>
+    <t>8조 5741억 4400만</t>
+  </si>
+  <si>
     <t>키우는건질색</t>
   </si>
   <si>
@@ -1337,22 +1355,13 @@
     <t>8조 4789억 5075만</t>
   </si>
   <si>
-    <t>강띵띵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%9D%B5%EB%9D%B5</t>
-  </si>
-  <si>
-    <t>8조 2123억 8705만</t>
-  </si>
-  <si>
     <t>악전</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%A0%84</t>
   </si>
   <si>
-    <t>6조 6792억 8468만</t>
+    <t>6조 9563억 9212만</t>
   </si>
   <si>
     <t>후아멀로하냐</t>
@@ -1385,7 +1394,7 @@
     <t>98</t>
   </si>
   <si>
-    <t>5조 2081억 4052만</t>
+    <t>5조 4430억 3652만</t>
   </si>
   <si>
     <t>술취한호랑이</t>
@@ -1397,22 +1406,22 @@
     <t>4조 8734억 8870만</t>
   </si>
   <si>
+    <t>수년</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%85%84</t>
+  </si>
+  <si>
+    <t>4조 3429억 3876만</t>
+  </si>
+  <si>
     <t>한Poll</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9CPoll</t>
   </si>
   <si>
-    <t>4조 299억 264만</t>
-  </si>
-  <si>
-    <t>수년</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%85%84</t>
-  </si>
-  <si>
-    <t>4조 64억 658만</t>
+    <t>4조 3050억 8452만</t>
   </si>
   <si>
     <t>김치왕뚜껑</t>
@@ -1430,7 +1439,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%8F%98%EC%95%BC%EB%A1%9C%EB%A1%9C</t>
   </si>
   <si>
-    <t>2조 4554억 6648만</t>
+    <t>2조 6663억 6952만</t>
   </si>
   <si>
     <t>치즈왕뚜껑</t>
@@ -1439,7 +1448,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%A6%88%EC%99%95%EB%9A%9C%EA%BB%91</t>
   </si>
   <si>
-    <t>2조 1657억 1197만</t>
+    <t>2조 1846억 5297만</t>
   </si>
   <si>
     <t>신궁쨩</t>
@@ -1457,7 +1466,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
   </si>
   <si>
-    <t>7161조 3638억 2994만</t>
+    <t>8423조 4010억 316만</t>
   </si>
   <si>
     <t>실민</t>
@@ -1466,7 +1475,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%EB%AF%BC</t>
   </si>
   <si>
-    <t>1079조 207억 5639만</t>
+    <t>1232조 428억 1327만</t>
   </si>
   <si>
     <t>약한고등어</t>
@@ -1484,7 +1493,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%8B%A4</t>
   </si>
   <si>
-    <t>623조 1792억 4623만</t>
+    <t>637조 9884억 704만</t>
   </si>
   <si>
     <t>앨삐</t>
@@ -1493,7 +1502,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EC%82%90</t>
   </si>
   <si>
-    <t>298조 4629억 4887만</t>
+    <t>317조 9218억 327만</t>
   </si>
   <si>
     <t>문디르</t>
@@ -1502,7 +1511,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
   </si>
   <si>
-    <t>206조 8757억 5344만</t>
+    <t>209조 3802억 6873만</t>
   </si>
   <si>
     <t>항상밝은하루</t>
@@ -1511,7 +1520,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AD%EC%83%81%EB%B0%9D%EC%9D%80%ED%95%98%EB%A3%A8</t>
   </si>
   <si>
-    <t>174조 1834억 1713만</t>
+    <t>198조 5777억 2328만</t>
   </si>
   <si>
     <t>비트츄</t>
@@ -1520,7 +1529,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%ED%8A%B8%EC%B8%84</t>
   </si>
   <si>
-    <t>124조 4229억 3053만</t>
+    <t>160조 5093억 7580만</t>
   </si>
   <si>
     <t>봉튜</t>
@@ -1547,7 +1556,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%8F%AC%EC%9D%98%EC%98%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>60조 752억 9194만</t>
+    <t>63조 6178억 2541만</t>
   </si>
   <si>
     <t>꽃나래</t>
@@ -1556,7 +1565,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
   </si>
   <si>
-    <t>44조 2729억 5365만</t>
+    <t>45조 2828억 2447만</t>
   </si>
   <si>
     <t>은달총</t>
@@ -1568,13 +1577,22 @@
     <t>38조 9416억 5281만</t>
   </si>
   <si>
+    <t>땩콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>25조 6837억 4377만</t>
+  </si>
+  <si>
     <t>김대협</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8C%80%ED%98%91</t>
   </si>
   <si>
-    <t>23조 6540억 5623만</t>
+    <t>24조 343억 8478만</t>
   </si>
   <si>
     <t>뽀라비</t>
@@ -1583,16 +1601,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
   </si>
   <si>
-    <t>22조 1068억 9929만</t>
-  </si>
-  <si>
-    <t>땩콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>21조 9833억 8948만</t>
+    <t>23조 7047억 968만</t>
   </si>
   <si>
     <t>에망</t>
@@ -1601,7 +1610,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
   </si>
   <si>
-    <t>12조 5545억 1110만</t>
+    <t>13조 6686억 9958만</t>
   </si>
   <si>
     <t>낭만만듀</t>
@@ -1610,7 +1619,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%EB%A7%8C%EB%93%80</t>
   </si>
   <si>
-    <t>10조 3682억 9319만</t>
+    <t>11조 4930억 9873만</t>
   </si>
   <si>
     <t>봄녘</t>
@@ -1619,7 +1628,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EB%85%98</t>
   </si>
   <si>
-    <t>8조 8066억 7996만</t>
+    <t>9조 3942억 2359만</t>
   </si>
   <si>
     <t>다송이</t>
@@ -1628,7 +1637,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
   </si>
   <si>
-    <t>7조 8427억 4237만</t>
+    <t>8조 6843억 7977만</t>
+  </si>
+  <si>
+    <t>봉합불가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>7조 1372억 9919만</t>
   </si>
   <si>
     <t>빠나딘</t>
@@ -1637,16 +1655,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EB%94%98</t>
   </si>
   <si>
-    <t>6조 8464억 1602만</t>
-  </si>
-  <si>
-    <t>봉합불가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>6조 7354억 3533만</t>
+    <t>7조 541억 2250만</t>
   </si>
   <si>
     <t>양카오너</t>
@@ -1658,7 +1667,7 @@
     <t>97</t>
   </si>
   <si>
-    <t>3조 3513억 5154만</t>
+    <t>3조 9612억 7314만</t>
   </si>
   <si>
     <t>강한고등어</t>
@@ -1676,16 +1685,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
   </si>
   <si>
+    <t>1조 449억 856만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
+  </si>
+  <si>
     <t>96</t>
   </si>
   <si>
-    <t>1조 206억 7862만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
-  </si>
-  <si>
-    <t>6421억 9963만</t>
+    <t>6424억 6751만</t>
   </si>
   <si>
     <t>용광사</t>
@@ -1697,7 +1706,7 @@
     <t>95</t>
   </si>
   <si>
-    <t>6011억 6649만</t>
+    <t>6354억 2182만</t>
   </si>
   <si>
     <t>비어치킨</t>
@@ -1709,7 +1718,7 @@
     <t>94</t>
   </si>
   <si>
-    <t>3653억 5893만</t>
+    <t>4074억 222만</t>
   </si>
 </sst>
 </file>
@@ -2446,13 +2455,13 @@
         <v>70</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2463,22 +2472,22 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>83</v>
@@ -2513,10 +2522,10 @@
         <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2527,28 +2536,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2559,25 +2568,25 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>100</v>
@@ -2594,16 +2603,16 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>104</v>
@@ -2641,7 +2650,7 @@
         <v>110</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>111</v>
@@ -2670,13 +2679,13 @@
         <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2687,28 +2696,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2719,28 +2728,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2751,25 +2760,25 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>129</v>
@@ -2798,10 +2807,10 @@
         <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>133</v>
@@ -2830,7 +2839,7 @@
         <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>137</v>
@@ -2862,7 +2871,7 @@
         <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>137</v>
@@ -2894,7 +2903,7 @@
         <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>137</v>
@@ -2926,7 +2935,7 @@
         <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>137</v>
@@ -2990,7 +2999,7 @@
         <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>159</v>
@@ -3054,7 +3063,7 @@
         <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>159</v>
@@ -3086,7 +3095,7 @@
         <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>159</v>
@@ -3118,7 +3127,7 @@
         <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>137</v>
@@ -3150,13 +3159,13 @@
         <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H25" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3170,25 +3179,25 @@
         <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3202,13 +3211,13 @@
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
@@ -3217,7 +3226,7 @@
         <v>154</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>188</v>
@@ -3246,7 +3255,7 @@
         <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>159</v>
@@ -3278,10 +3287,10 @@
         <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>195</v>
@@ -3310,10 +3319,10 @@
         <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>199</v>
@@ -3342,10 +3351,10 @@
         <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>203</v>
@@ -3494,7 +3503,7 @@
         <v>71</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>209</v>
@@ -3508,7 +3517,7 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>210</v>
@@ -3523,10 +3532,10 @@
         <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>212</v>
@@ -3555,10 +3564,10 @@
         <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>215</v>
@@ -3572,7 +3581,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>216</v>
@@ -3587,10 +3596,10 @@
         <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>218</v>
@@ -3604,7 +3613,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>219</v>
@@ -3619,10 +3628,10 @@
         <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>221</v>
@@ -3651,10 +3660,10 @@
         <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>224</v>
@@ -3683,10 +3692,10 @@
         <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>227</v>
@@ -3715,7 +3724,7 @@
         <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>137</v>
@@ -3732,7 +3741,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>231</v>
@@ -3747,7 +3756,7 @@
         <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>137</v>
@@ -3764,7 +3773,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>234</v>
@@ -3779,7 +3788,7 @@
         <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>159</v>
@@ -3796,7 +3805,7 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>237</v>
@@ -3811,7 +3820,7 @@
         <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>137</v>
@@ -3843,7 +3852,7 @@
         <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>137</v>
@@ -3875,7 +3884,7 @@
         <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>137</v>
@@ -3907,10 +3916,10 @@
         <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>248</v>
@@ -3939,7 +3948,7 @@
         <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>159</v>
@@ -3971,7 +3980,7 @@
         <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>137</v>
@@ -4003,7 +4012,7 @@
         <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>164</v>
@@ -4035,10 +4044,10 @@
         <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>260</v>
@@ -4067,7 +4076,7 @@
         <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>159</v>
@@ -4102,7 +4111,7 @@
         <v>104</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>266</v>
@@ -4131,7 +4140,7 @@
         <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>164</v>
@@ -4163,10 +4172,10 @@
         <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>272</v>
@@ -4192,10 +4201,10 @@
         <v>273</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>164</v>
@@ -4227,10 +4236,10 @@
         <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>277</v>
@@ -4259,10 +4268,10 @@
         <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>280</v>
@@ -4291,10 +4300,10 @@
         <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>283</v>
@@ -4323,10 +4332,10 @@
         <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>286</v>
@@ -4355,7 +4364,7 @@
         <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>164</v>
@@ -4387,7 +4396,7 @@
         <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>164</v>
@@ -4439,7 +4448,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4504,7 +4513,7 @@
         <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>295</v>
@@ -4533,13 +4542,13 @@
         <v>297</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>71</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>298</v>
@@ -4553,7 +4562,7 @@
         <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>299</v>
@@ -4568,10 +4577,10 @@
         <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>301</v>
@@ -4600,10 +4609,10 @@
         <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>304</v>
@@ -4617,7 +4626,7 @@
         <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>305</v>
@@ -4632,10 +4641,10 @@
         <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>307</v>
@@ -4649,7 +4658,7 @@
         <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>308</v>
@@ -4664,10 +4673,10 @@
         <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>310</v>
@@ -4696,10 +4705,10 @@
         <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>313</v>
@@ -4728,10 +4737,10 @@
         <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>316</v>
@@ -4760,10 +4769,10 @@
         <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>319</v>
@@ -4777,7 +4786,7 @@
         <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>320</v>
@@ -4792,10 +4801,10 @@
         <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>322</v>
@@ -4809,7 +4818,7 @@
         <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>323</v>
@@ -4824,7 +4833,7 @@
         <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>159</v>
@@ -4841,7 +4850,7 @@
         <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>326</v>
@@ -4856,7 +4865,7 @@
         <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>159</v>
@@ -4888,10 +4897,10 @@
         <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>331</v>
@@ -4920,10 +4929,10 @@
         <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>334</v>
@@ -4952,10 +4961,10 @@
         <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>337</v>
@@ -4984,7 +4993,7 @@
         <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>164</v>
@@ -5048,10 +5057,10 @@
         <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>346</v>
@@ -5080,7 +5089,7 @@
         <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>164</v>
@@ -5112,10 +5121,10 @@
         <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>352</v>
@@ -5144,7 +5153,7 @@
         <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>164</v>
@@ -5176,7 +5185,7 @@
         <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>358</v>
@@ -5208,10 +5217,10 @@
         <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>358</v>
+        <v>164</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>362</v>
@@ -5240,13 +5249,13 @@
         <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5260,22 +5269,22 @@
         <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>369</v>
@@ -5304,7 +5313,7 @@
         <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>358</v>
@@ -5336,10 +5345,10 @@
         <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>375</v>
@@ -5368,10 +5377,10 @@
         <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>378</v>
@@ -5380,8 +5389,40 @@
         <v>24</v>
       </c>
     </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -5411,6 +5452,7 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5427,7 +5469,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5477,19 +5519,19 @@
         <v>48</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>295</v>
+        <v>383</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5503,13 +5545,13 @@
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>70</v>
@@ -5518,10 +5560,10 @@
         <v>110</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>383</v>
+        <v>295</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5532,16 +5574,16 @@
         <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
@@ -5553,7 +5595,7 @@
         <v>105</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5567,13 +5609,13 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
@@ -5582,10 +5624,10 @@
         <v>71</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5596,28 +5638,28 @@
         <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>137</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5628,28 +5670,28 @@
         <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5663,13 +5705,13 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
@@ -5678,10 +5720,10 @@
         <v>110</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5695,25 +5737,25 @@
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5727,25 +5769,25 @@
         <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>137</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5756,28 +5798,28 @@
         <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5788,28 +5830,28 @@
         <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5820,28 +5862,28 @@
         <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>358</v>
+        <v>164</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5855,25 +5897,25 @@
         <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5887,25 +5929,25 @@
         <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>358</v>
+        <v>164</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5919,25 +5961,25 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5951,25 +5993,25 @@
         <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5983,25 +6025,25 @@
         <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6015,25 +6057,25 @@
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6047,25 +6089,25 @@
         <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6079,25 +6121,25 @@
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6111,13 +6153,13 @@
         <v>166</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
@@ -6126,10 +6168,10 @@
         <v>110</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6143,13 +6185,13 @@
         <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
@@ -6158,10 +6200,10 @@
         <v>110</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6175,25 +6217,25 @@
         <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6207,13 +6249,13 @@
         <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>70</v>
@@ -6222,10 +6264,10 @@
         <v>71</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6239,25 +6281,25 @@
         <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6271,13 +6313,13 @@
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
@@ -6286,10 +6328,10 @@
         <v>88</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>444</v>
+        <v>365</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6303,25 +6345,25 @@
         <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>368</v>
+        <v>447</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6335,25 +6377,25 @@
         <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6367,25 +6409,25 @@
         <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6399,25 +6441,25 @@
         <v>200</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6516,25 +6558,25 @@
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>295</v>
+        <v>383</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6548,13 +6590,13 @@
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>70</v>
@@ -6563,10 +6605,10 @@
         <v>71</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6577,28 +6619,28 @@
         <v>49</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6612,13 +6654,13 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
@@ -6627,10 +6669,10 @@
         <v>110</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6641,28 +6683,28 @@
         <v>49</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>105</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6673,28 +6715,28 @@
         <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6708,13 +6750,13 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
@@ -6726,7 +6768,7 @@
         <v>137</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6740,13 +6782,13 @@
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
@@ -6755,10 +6797,10 @@
         <v>71</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6772,13 +6814,13 @@
         <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
@@ -6787,10 +6829,10 @@
         <v>71</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6801,28 +6843,28 @@
         <v>49</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>137</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6833,16 +6875,16 @@
         <v>49</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
@@ -6851,10 +6893,10 @@
         <v>71</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6865,16 +6907,16 @@
         <v>49</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
@@ -6883,10 +6925,10 @@
         <v>110</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6900,13 +6942,13 @@
         <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
@@ -6915,10 +6957,10 @@
         <v>110</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6932,13 +6974,13 @@
         <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
@@ -6947,10 +6989,10 @@
         <v>163</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6964,25 +7006,25 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6996,25 +7038,25 @@
         <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>358</v>
+        <v>187</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7028,25 +7070,25 @@
         <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7060,25 +7102,25 @@
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7092,25 +7134,25 @@
         <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7124,13 +7166,13 @@
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
@@ -7139,10 +7181,10 @@
         <v>110</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7156,13 +7198,13 @@
         <v>166</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
@@ -7171,10 +7213,10 @@
         <v>110</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7188,25 +7230,25 @@
         <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7220,25 +7262,25 @@
         <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7252,25 +7294,25 @@
         <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7284,13 +7326,13 @@
         <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
@@ -7299,10 +7341,10 @@
         <v>163</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7316,25 +7358,25 @@
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7354,19 +7396,19 @@
         <v>58</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>71</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7380,13 +7422,13 @@
         <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>70</v>
@@ -7395,10 +7437,10 @@
         <v>71</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7412,25 +7454,25 @@
         <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>

--- a/reports/셀린느/셀린느_mgf_matched_5_guilds.xlsx
+++ b/reports/셀린느/셀린느_mgf_matched_5_guilds.xlsx
@@ -296,7 +296,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>2183조 6870억 5466만</t>
+    <t>2194조 4949억 8899만</t>
   </si>
   <si>
     <t>5</t>
@@ -386,7 +386,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%88%EA%BD%83%EC%B2%B4%EB%A6%AC</t>
   </si>
   <si>
-    <t>500조 7087억 496만</t>
+    <t>502조 6372억 1549만</t>
   </si>
   <si>
     <t>11</t>
@@ -401,7 +401,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>417조 4654억 638만</t>
+    <t>439조 4475억 1469만</t>
   </si>
   <si>
     <t>12</t>
@@ -536,7 +536,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%A7%80%EC%97%B0</t>
   </si>
   <si>
-    <t>115조 1259억 5158만</t>
+    <t>115조 2976억 5319만</t>
   </si>
   <si>
     <t>22</t>
@@ -638,7 +638,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B0%EB%8C%80%EA%B3%A4%EC%A4%84%EB%B0%95%EC%9D%B4</t>
   </si>
   <si>
-    <t>33조 5705억 4164만</t>
+    <t>35조 2232억 1959만</t>
   </si>
   <si>
     <t>스타냥이</t>
@@ -1451,6 +1451,15 @@
     <t>2조 1846억 5297만</t>
   </si>
   <si>
+    <t>싸뤽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
+  </si>
+  <si>
+    <t>9288조 7988억 1546만</t>
+  </si>
+  <si>
     <t>신궁쨩</t>
   </si>
   <si>
@@ -1460,15 +1469,6 @@
     <t>8668조 7855억 1234만</t>
   </si>
   <si>
-    <t>싸뤽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
-  </si>
-  <si>
-    <t>8423조 4010억 316만</t>
-  </si>
-  <si>
     <t>실민</t>
   </si>
   <si>
@@ -1478,6 +1478,15 @@
     <t>1232조 428억 1327만</t>
   </si>
   <si>
+    <t>민실</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%8B%A4</t>
+  </si>
+  <si>
+    <t>760조 7667억 2010만</t>
+  </si>
+  <si>
     <t>약한고등어</t>
   </si>
   <si>
@@ -1487,15 +1496,6 @@
     <t>732조 9186억 8857만</t>
   </si>
   <si>
-    <t>민실</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%8B%A4</t>
-  </si>
-  <si>
-    <t>637조 9884억 704만</t>
-  </si>
-  <si>
     <t>앨삐</t>
   </si>
   <si>
@@ -1556,7 +1556,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%8F%AC%EC%9D%98%EC%98%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>63조 6178억 2541만</t>
+    <t>66조 6160억 1431만</t>
   </si>
   <si>
     <t>꽃나래</t>
@@ -1586,6 +1586,15 @@
     <t>25조 6837억 4377만</t>
   </si>
   <si>
+    <t>뽀라비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
+  </si>
+  <si>
+    <t>24조 1275억 9609만</t>
+  </si>
+  <si>
     <t>김대협</t>
   </si>
   <si>
@@ -1593,15 +1602,6 @@
   </si>
   <si>
     <t>24조 343억 8478만</t>
-  </si>
-  <si>
-    <t>뽀라비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
-  </si>
-  <si>
-    <t>23조 7047억 968만</t>
   </si>
   <si>
     <t>에망</t>
@@ -6570,7 +6570,7 @@
         <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>383</v>
@@ -6602,10 +6602,10 @@
         <v>70</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>83</v>
+        <v>383</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>479</v>
@@ -6666,10 +6666,10 @@
         <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>485</v>
@@ -6698,10 +6698,10 @@
         <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>488</v>
@@ -7050,10 +7050,10 @@
         <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>187</v>
+        <v>365</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>521</v>
@@ -7082,10 +7082,10 @@
         <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>365</v>
+        <v>187</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>524</v>
